--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.985</v>
+        <v>0.9849</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0843</v>
+        <v>1.0816</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9798</v>
+        <v>0.98</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2628</v>
+        <v>1.2587</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.6755</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9343</v>
+        <v>0.9619</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3847</v>
+        <v>1.943</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.9225</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9745</v>
+        <v>0.9734</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6229</v>
+        <v>1.6337</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4.3624</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9745</v>
+        <v>0.9749</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6232</v>
+        <v>1.6027</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4.376</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9448</v>
+        <v>0.9452</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3087</v>
+        <v>2.3034</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5.1503</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8504</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2886</v>
+        <v>3.2896</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>5.188</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>0.9825</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2665</v>
+        <v>1.2608</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.9185</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8504</v>
       </c>
       <c r="F10" t="n">
-        <v>3.295</v>
+        <v>3.294</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5.1835</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8627</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1863</v>
+        <v>3.1892</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5.1816</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8484</v>
+        <v>0.8482</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3072</v>
+        <v>3.3086</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5.1834</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8491</v>
+        <v>0.8492</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2995</v>
+        <v>3.2992</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.1901</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8635</v>
+        <v>0.8632</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1799</v>
+        <v>3.1828</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5.1839</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8486</v>
+        <v>0.9112</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3042</v>
+        <v>2.7259</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5.1802</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.9129</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3014</v>
+        <v>2.715</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8623</v>
+        <v>0.9356</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1876</v>
+        <v>2.3959</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>5.1812</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9649</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9152</v>
+        <v>1.9121</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4.5428</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.969</v>
+        <v>0.9688</v>
       </c>
       <c r="F19" t="n">
-        <v>1.913</v>
+        <v>1.9149</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4.783</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9601</v>
+        <v>0.9603</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0167</v>
+        <v>2.0164</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>4.795</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9557</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1611</v>
+        <v>2.1601</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4.838</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9574</v>
+        <v>0.9577</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1385</v>
+        <v>2.1327</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4.8253</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9543</v>
+        <v>0.9535</v>
       </c>
       <c r="F23" t="n">
-        <v>2.13</v>
+        <v>2.143</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>4.817</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.955</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1342</v>
+        <v>2.1542</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4.8349</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9543</v>
+        <v>0.9546</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1504</v>
+        <v>2.148</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4.8634</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9687</v>
+        <v>0.9764</v>
       </c>
       <c r="F26" t="n">
-        <v>1.887</v>
+        <v>1.712</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4.6928</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9515</v>
+        <v>0.9507</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2166</v>
+        <v>2.2122</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>4.6079</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9463</v>
+        <v>0.9673</v>
       </c>
       <c r="F28" t="n">
-        <v>2.2716</v>
+        <v>1.9087</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>4.6311</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9759</v>
+        <v>0.9756</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7077</v>
+        <v>1.7059</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4.6827</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9595</v>
       </c>
       <c r="F30" t="n">
-        <v>2.1282</v>
+        <v>2.1264</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4.7834</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9714</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7794</v>
+        <v>1.7847</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4.8294</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9667</v>
+        <v>0.9673</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9056</v>
+        <v>1.9063</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4.767</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9664</v>
+        <v>0.9666</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9005</v>
+        <v>1.8954</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4.7066</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9833</v>
+        <v>0.9724</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3572</v>
+        <v>1.608</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3.4386</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9835</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2241</v>
+        <v>1.3256</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3.3232</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.983</v>
+        <v>0.9832</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3258</v>
+        <v>1.3227</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>3.3066</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9805</v>
+        <v>0.9808</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3579</v>
+        <v>1.354</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3.3595</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9807</v>
+        <v>0.9809</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3829</v>
+        <v>1.385</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3.4096</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9819</v>
+        <v>0.963</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2788</v>
+        <v>1.7171</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3.3254</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.978</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7431</v>
+        <v>1.4509</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>3.498</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>0.9841</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3211</v>
+        <v>1.3214</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3.3233</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9846</v>
+        <v>0.9871</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2269</v>
+        <v>1.1369</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>3.0795</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9846</v>
+        <v>0.985</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2479</v>
+        <v>1.2408</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>3.0913</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9822</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3059</v>
+        <v>1.301</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>3.2639</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9809</v>
+        <v>0.9839</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3778</v>
+        <v>1.2787</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3.4033</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9646</v>
+        <v>0.9649</v>
       </c>
       <c r="F46" t="n">
-        <v>1.7109</v>
+        <v>1.7082</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3.3873</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9805</v>
+        <v>0.9804</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3801</v>
+        <v>1.379</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3.4396</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9787</v>
+        <v>0.98</v>
       </c>
       <c r="F48" t="n">
-        <v>1.6324</v>
+        <v>1.6115</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>4.3208</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9756</v>
+        <v>0.9757</v>
       </c>
       <c r="F49" t="n">
-        <v>1.5044</v>
+        <v>1.504</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>3.1081</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>0.9865</v>
       </c>
       <c r="F50" t="n">
-        <v>1.0597</v>
+        <v>1.0588</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2.644</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>0.9655</v>
       </c>
       <c r="F51" t="n">
-        <v>1.5512</v>
+        <v>1.5504</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2.9866</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9654</v>
+        <v>0.9655</v>
       </c>
       <c r="F52" t="n">
-        <v>1.549</v>
+        <v>1.5478</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2.9527</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9871</v>
+        <v>0.9849</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9726</v>
+        <v>1.0649</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2.5701</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9827</v>
+        <v>0.9829</v>
       </c>
       <c r="F54" t="n">
-        <v>1.1171</v>
+        <v>1.1067</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2.5496</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9717</v>
+        <v>0.9715</v>
       </c>
       <c r="F55" t="n">
-        <v>1.4053</v>
+        <v>1.4097</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2.769</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9868</v>
+        <v>0.985</v>
       </c>
       <c r="F56" t="n">
-        <v>1.0284</v>
+        <v>1.0897</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2.755</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9869</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>1.0121</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2.7262</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9756</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>1.6002</v>
+        <v>1.6073</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>4.3922</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9756</v>
+        <v>0.9747</v>
       </c>
       <c r="F59" t="n">
-        <v>1.6032</v>
+        <v>1.6163</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>4.3742</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9751</v>
+        <v>0.9737</v>
       </c>
       <c r="F60" t="n">
-        <v>1.611</v>
+        <v>1.6288</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>4.3705</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9741</v>
+        <v>0.9737</v>
       </c>
       <c r="F61" t="n">
-        <v>1.6315</v>
+        <v>1.6455</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>4.3819</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9796</v>
+        <v>0.9797</v>
       </c>
       <c r="F62" t="n">
-        <v>1.2081</v>
+        <v>1.206</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2.7376</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9678</v>
+        <v>0.9677</v>
       </c>
       <c r="F63" t="n">
-        <v>1.4834</v>
+        <v>1.485</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2.7917</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9665</v>
+        <v>0.9667</v>
       </c>
       <c r="F64" t="n">
-        <v>1.511</v>
+        <v>1.5082</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2.7982</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9696</v>
+        <v>0.9695</v>
       </c>
       <c r="F65" t="n">
-        <v>1.4542</v>
+        <v>1.4576</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2.752</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9865</v>
       </c>
       <c r="F66" t="n">
-        <v>1.0747</v>
+        <v>1.0715</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9747</v>
+        <v>0.9749</v>
       </c>
       <c r="F67" t="n">
-        <v>1.3566</v>
+        <v>1.3549</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2.7185</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>0.9757</v>
       </c>
       <c r="F68" t="n">
-        <v>1.3516</v>
+        <v>1.3549</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2.7346</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>0.9714</v>
       </c>
       <c r="F69" t="n">
-        <v>1.8082</v>
+        <v>1.8031</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>4.5337</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9701</v>
+        <v>0.9699</v>
       </c>
       <c r="F70" t="n">
-        <v>1.8418</v>
+        <v>1.8486</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>4.5839</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9782</v>
+        <v>0.9778</v>
       </c>
       <c r="F71" t="n">
-        <v>1.6733</v>
+        <v>1.7019</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>4.5278</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9678</v>
+        <v>0.9679</v>
       </c>
       <c r="F72" t="n">
-        <v>1.8471</v>
+        <v>1.8539</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>4.4641</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9836</v>
+        <v>0.9839</v>
       </c>
       <c r="F73" t="n">
-        <v>1.3701</v>
+        <v>1.3647</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>3.615</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>0.9787</v>
       </c>
       <c r="F74" t="n">
-        <v>1.5117</v>
+        <v>1.5152</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3.8098</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>0.8844</v>
       </c>
       <c r="F75" t="n">
-        <v>2.9951</v>
+        <v>2.9984</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>5.1883</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>0.8844</v>
       </c>
       <c r="F76" t="n">
-        <v>2.9951</v>
+        <v>2.9984</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>5.1883</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>0.9656</v>
       </c>
       <c r="F77" t="n">
-        <v>1.8466</v>
+        <v>1.846</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>4.4512</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9643</v>
+        <v>0.9639</v>
       </c>
       <c r="F78" t="n">
-        <v>1.8738</v>
+        <v>1.8777</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>4.4567</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9544</v>
+        <v>0.9546</v>
       </c>
       <c r="F79" t="n">
-        <v>2.076</v>
+        <v>2.0696</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>4.4444</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9639</v>
       </c>
       <c r="F80" t="n">
-        <v>1.8773</v>
+        <v>1.8797</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>4.4538</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9699</v>
+        <v>0.97</v>
       </c>
       <c r="F81" t="n">
-        <v>1.4516</v>
+        <v>1.4504</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2.7859</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9692</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>1.4619</v>
+        <v>1.4603</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2.7946</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8872</v>
+        <v>0.8873</v>
       </c>
       <c r="F83" t="n">
-        <v>2.974</v>
+        <v>2.9791</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>5.195</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8862</v>
+        <v>0.8863</v>
       </c>
       <c r="F84" t="n">
-        <v>2.9739</v>
+        <v>2.9797</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>5.1939</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8874</v>
+        <v>0.8875</v>
       </c>
       <c r="F85" t="n">
-        <v>2.975</v>
+        <v>2.9799</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>5.2031</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9761</v>
+        <v>0.9728</v>
       </c>
       <c r="F86" t="n">
-        <v>1.7161</v>
+        <v>1.8328</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>4.5759</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9742</v>
+        <v>0.9673</v>
       </c>
       <c r="F87" t="n">
-        <v>1.845</v>
+        <v>1.973</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>4.6122</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9744</v>
+        <v>0.974</v>
       </c>
       <c r="F88" t="n">
-        <v>1.8218</v>
+        <v>1.8187</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>4.5301</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9659</v>
+        <v>0.9648</v>
       </c>
       <c r="F89" t="n">
-        <v>1.8776</v>
+        <v>1.8971</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>4.4727</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9846</v>
+        <v>0.985</v>
       </c>
       <c r="F90" t="n">
-        <v>1.2476</v>
+        <v>1.2404</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>3.092</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9823</v>
+        <v>0.9825</v>
       </c>
       <c r="F91" t="n">
-        <v>1.303</v>
+        <v>1.2984</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>3.2639</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9744</v>
+        <v>0.974</v>
       </c>
       <c r="F92" t="n">
-        <v>1.8218</v>
+        <v>1.8187</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>4.5301</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9823</v>
+        <v>0.9825</v>
       </c>
       <c r="F93" t="n">
-        <v>1.303</v>
+        <v>1.2984</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>3.2639</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9343</v>
+        <v>0.9619</v>
       </c>
       <c r="F94" t="n">
-        <v>2.3847</v>
+        <v>1.943</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>4.9225</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.825</v>
+        <v>0.8259</v>
       </c>
       <c r="F95" t="n">
-        <v>3.5513</v>
+        <v>3.5474</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>5.3554</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
         <v>0.9332</v>
       </c>
       <c r="F96" t="n">
-        <v>2.3864</v>
+        <v>2.3877</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>4.9189</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9213</v>
+        <v>0.9216</v>
       </c>
       <c r="F97" t="n">
-        <v>2.4832</v>
+        <v>2.4825</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>4.9159</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9465</v>
+        <v>0.9469</v>
       </c>
       <c r="F98" t="n">
-        <v>2.0336</v>
+        <v>2.0304</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>3.9664</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9588</v>
+        <v>0.9595</v>
       </c>
       <c r="F99" t="n">
-        <v>1.7734</v>
+        <v>1.763</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>3.9908</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9563</v>
+        <v>0.956</v>
       </c>
       <c r="F100" t="n">
-        <v>1.8323</v>
+        <v>1.8348</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>3.9943</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9706</v>
+        <v>0.9708</v>
       </c>
       <c r="F101" t="n">
-        <v>1.5574</v>
+        <v>1.5701</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>4.0831</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9705</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>1.5857</v>
+        <v>1.8081</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>4.1386</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9691</v>
+        <v>0.9506</v>
       </c>
       <c r="F103" t="n">
-        <v>1.6494</v>
+        <v>1.9837</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>4.0577</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9439</v>
+        <v>0.944</v>
       </c>
       <c r="F104" t="n">
-        <v>2.0432</v>
+        <v>2.0428</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>3.9648</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9435</v>
+        <v>0.9395</v>
       </c>
       <c r="F105" t="n">
-        <v>2.0424</v>
+        <v>2.0955</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9613</v>
+        <v>0.9615</v>
       </c>
       <c r="F106" t="n">
-        <v>1.7494</v>
+        <v>1.7467</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>4.0159</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9626</v>
+        <v>0.9588</v>
       </c>
       <c r="F107" t="n">
-        <v>1.7333</v>
+        <v>1.7934</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>4.0527</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.974</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>1.5978</v>
+        <v>1.6148</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>3.9548</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9721</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>1.5709</v>
+        <v>1.5684</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>3.8942</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9718</v>
+        <v>0.972</v>
       </c>
       <c r="F110" t="n">
-        <v>1.6041</v>
+        <v>1.5976</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>3.9389</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9559</v>
+        <v>0.956</v>
       </c>
       <c r="F111" t="n">
-        <v>1.8766</v>
+        <v>1.877</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>3.8139</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9836</v>
+        <v>0.9789</v>
       </c>
       <c r="F112" t="n">
-        <v>1.2933</v>
+        <v>1.4349</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>3.5458</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9791</v>
+        <v>0.9792</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3954</v>
+        <v>1.3957</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>3.6341</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9724</v>
       </c>
       <c r="F114" t="n">
-        <v>1.5866</v>
+        <v>1.5799</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>3.8757</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9562</v>
       </c>
       <c r="F115" t="n">
-        <v>1.8711</v>
+        <v>1.871</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3.8219</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9819</v>
+        <v>0.966</v>
       </c>
       <c r="F116" t="n">
-        <v>1.1697</v>
+        <v>1.5298</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>2.8087</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9823</v>
+        <v>0.9789</v>
       </c>
       <c r="F117" t="n">
-        <v>1.1686</v>
+        <v>1.2371</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2.8115</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9435</v>
+        <v>0.9395</v>
       </c>
       <c r="F118" t="n">
-        <v>2.0424</v>
+        <v>2.0955</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9791</v>
+        <v>0.9792</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3954</v>
+        <v>1.3957</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>3.6341</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9003</v>
+        <v>0.9005</v>
       </c>
       <c r="F120" t="n">
-        <v>2.6959</v>
+        <v>2.6965</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>5.0107</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9003</v>
+        <v>0.9005</v>
       </c>
       <c r="F121" t="n">
-        <v>2.6959</v>
+        <v>2.6965</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>5.0107</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9265</v>
+        <v>0.925</v>
       </c>
       <c r="F122" t="n">
-        <v>2.3615</v>
+        <v>2.3774</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>4.4583</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.979</v>
+        <v>0.9791</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3967</v>
+        <v>1.3968</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9751</v>
+        <v>0.9765</v>
       </c>
       <c r="F124" t="n">
-        <v>1.4949</v>
+        <v>1.4713</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>3.6725</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.8611</v>
+        <v>0.9338</v>
       </c>
       <c r="F125" t="n">
-        <v>3.0854</v>
+        <v>2.3725</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>4.926</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8844</v>
+        <v>0.8822</v>
       </c>
       <c r="F126" t="n">
-        <v>2.9494</v>
+        <v>2.969</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>4.9958</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9831</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F127" t="n">
-        <v>1.1561</v>
+        <v>1.3453</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>3.2713</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.8746</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>3.0629</v>
+        <v>3.0644</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>5.0209</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8825</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>2.9587</v>
+        <v>2.9585</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>5.012</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E130" t="n">
         <v>0.8818</v>
       </c>
       <c r="F130" t="n">
-        <v>2.9674</v>
+        <v>2.9664</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>5.0105</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.8787</v>
+        <v>0.8784</v>
       </c>
       <c r="F131" t="n">
-        <v>2.996</v>
+        <v>2.9992</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>4.9844</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.8796</v>
+        <v>0.8797</v>
       </c>
       <c r="F132" t="n">
         <v>2.9788</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>5.0217</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8575</v>
+        <v>0.8746</v>
       </c>
       <c r="F133" t="n">
-        <v>3.209</v>
+        <v>3.068</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>5.0416</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E134" t="n">
         <v>0.8843</v>
       </c>
       <c r="F134" t="n">
-        <v>2.954</v>
+        <v>2.9551</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>5.0227</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E135" t="n">
         <v>0.8748</v>
       </c>
       <c r="F135" t="n">
-        <v>3.064</v>
+        <v>3.0649</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>5.0207</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.8788</v>
+        <v>0.8786</v>
       </c>
       <c r="F136" t="n">
-        <v>2.9906</v>
+        <v>2.9933</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>4.9803</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9647</v>
+        <v>0.9645</v>
       </c>
       <c r="F137" t="n">
-        <v>1.9385</v>
+        <v>1.9431</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>4.769</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9626</v>
+        <v>0.9627</v>
       </c>
       <c r="F138" t="n">
-        <v>1.9634</v>
+        <v>1.9674</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>4.5695</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9528</v>
+        <v>0.952</v>
       </c>
       <c r="F139" t="n">
-        <v>2.1406</v>
+        <v>2.1509</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>4.7985</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9707</v>
+        <v>0.971</v>
       </c>
       <c r="F140" t="n">
-        <v>1.6079</v>
+        <v>1.6048</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>3.3773</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9839</v>
+        <v>0.985</v>
       </c>
       <c r="F141" t="n">
-        <v>1.342</v>
+        <v>1.2809</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>3.4213</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9626</v>
+        <v>0.9627</v>
       </c>
       <c r="F142" t="n">
-        <v>1.9634</v>
+        <v>1.9674</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>4.5695</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9345</v>
+        <v>0.9346</v>
       </c>
       <c r="F143" t="n">
-        <v>2.4239</v>
+        <v>2.423</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>4.7677</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9706</v>
       </c>
       <c r="F144" t="n">
-        <v>1.7705</v>
+        <v>1.7568</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>4.7397</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9839</v>
+        <v>0.985</v>
       </c>
       <c r="F145" t="n">
-        <v>1.342</v>
+        <v>1.2809</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>3.4213</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.978</v>
+        <v>0.9721</v>
       </c>
       <c r="F146" t="n">
-        <v>1.3209</v>
+        <v>1.4527</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>3.2518</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9826</v>
       </c>
       <c r="F147" t="n">
-        <v>1.1825</v>
+        <v>1.1804</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>3.2395</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.9828</v>
+        <v>0.9779</v>
       </c>
       <c r="F148" t="n">
-        <v>1.1812</v>
+        <v>1.3279</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>3.2568</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.982</v>
+        <v>0.9772</v>
       </c>
       <c r="F149" t="n">
-        <v>1.1875</v>
+        <v>1.3481</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>3.2857</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.9784</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F150" t="n">
-        <v>1.32</v>
+        <v>1.3216</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>3.2596</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.9782</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F151" t="n">
-        <v>1.3202</v>
+        <v>1.3179</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>3.263</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.9781</v>
+        <v>0.9836</v>
       </c>
       <c r="F152" t="n">
-        <v>1.3222</v>
+        <v>1.1445</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>3.2344</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.9781</v>
+        <v>0.9842</v>
       </c>
       <c r="F153" t="n">
-        <v>1.3248</v>
+        <v>1.1358</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>3.2475</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.9825</v>
+        <v>0.9741</v>
       </c>
       <c r="F154" t="n">
-        <v>1.1742</v>
+        <v>1.4144</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>3.2529</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9678</v>
+        <v>0.9676</v>
       </c>
       <c r="F155" t="n">
-        <v>1.4837</v>
+        <v>1.4842</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>2.8228</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9853</v>
       </c>
       <c r="F156" t="n">
-        <v>1.0308</v>
+        <v>1.0314</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>2.7964</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9791</v>
+        <v>0.9847</v>
       </c>
       <c r="F157" t="n">
-        <v>1.2061</v>
+        <v>1.0346</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>2.7726</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9756</v>
+        <v>0.9757</v>
       </c>
       <c r="F158" t="n">
-        <v>1.33</v>
+        <v>1.3282</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>2.7111</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8823</v>
+        <v>0.8824</v>
       </c>
       <c r="F159" t="n">
-        <v>3.0305</v>
+        <v>3.0298</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>5.0451</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
         <v>0.9752</v>
       </c>
       <c r="F160" t="n">
-        <v>1.5238</v>
+        <v>1.5211</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>3.6229</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.9746</v>
+        <v>0.9756</v>
       </c>
       <c r="F161" t="n">
-        <v>1.5275</v>
+        <v>1.5019</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>3.6188</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.8807</v>
+        <v>0.8917</v>
       </c>
       <c r="F162" t="n">
-        <v>3.0449</v>
+        <v>2.8866</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>5.0614</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9726</v>
+        <v>0.9722</v>
       </c>
       <c r="F163" t="n">
-        <v>1.7768</v>
+        <v>1.8066</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>4.6095</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9706</v>
+        <v>0.9708</v>
       </c>
       <c r="F164" t="n">
-        <v>1.6082</v>
+        <v>1.6055</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>3.3775</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.8611</v>
+        <v>0.9338</v>
       </c>
       <c r="F165" t="n">
-        <v>3.0854</v>
+        <v>2.3725</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>4.926</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.9618</v>
+        <v>0.9615</v>
       </c>
       <c r="F166" t="n">
-        <v>2.0961</v>
+        <v>2.1027</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>5.3637</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9711</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F167" t="n">
-        <v>1.7557</v>
+        <v>1.7323</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>4.561</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9731</v>
       </c>
       <c r="F168" t="n">
-        <v>1.5413</v>
+        <v>1.5537</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>3.2664</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9851</v>
+        <v>0.9853</v>
       </c>
       <c r="F169" t="n">
-        <v>1.0898</v>
+        <v>1.0888</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>2.7066</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9712</v>
+        <v>0.971</v>
       </c>
       <c r="F170" t="n">
-        <v>1.8099</v>
+        <v>1.8154</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>3.8368</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9811</v>
+        <v>0.9812</v>
       </c>
       <c r="F171" t="n">
-        <v>1.2699</v>
+        <v>1.2732</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>3.0612</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9698</v>
+        <v>0.9645</v>
       </c>
       <c r="F172" t="n">
-        <v>1.7846</v>
+        <v>1.9133</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>4.7066</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9849</v>
       </c>
       <c r="F2" t="n">
+        <v>1.2258</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.0816</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2.655</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.98</v>
       </c>
       <c r="F3" t="n">
+        <v>1.2293</v>
+      </c>
+      <c r="G3" t="n">
         <v>1.2587</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2.6755</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9619</v>
       </c>
       <c r="F4" t="n">
+        <v>1.7763</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.943</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4.9225</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.9734</v>
       </c>
       <c r="F5" t="n">
+        <v>1.6097</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.6337</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4.3624</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.9749</v>
       </c>
       <c r="F6" t="n">
+        <v>1.6135</v>
+      </c>
+      <c r="G6" t="n">
         <v>1.6027</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4.376</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.9452</v>
       </c>
       <c r="F7" t="n">
+        <v>1.8498</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.3034</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>5.1503</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.8502999999999999</v>
       </c>
       <c r="F8" t="n">
+        <v>1.8623</v>
+      </c>
+      <c r="G8" t="n">
         <v>3.2896</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5.188</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9825</v>
       </c>
       <c r="F9" t="n">
+        <v>1.2729</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.2608</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2.9185</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.8504</v>
       </c>
       <c r="F10" t="n">
+        <v>1.8608</v>
+      </c>
+      <c r="G10" t="n">
         <v>3.294</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>5.1835</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.8624000000000001</v>
       </c>
       <c r="F11" t="n">
+        <v>1.8602</v>
+      </c>
+      <c r="G11" t="n">
         <v>3.1892</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>5.1816</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.8482</v>
       </c>
       <c r="F12" t="n">
+        <v>1.8608</v>
+      </c>
+      <c r="G12" t="n">
         <v>3.3086</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>5.1834</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.8492</v>
       </c>
       <c r="F13" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="G13" t="n">
         <v>3.2992</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>5.1901</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.8632</v>
       </c>
       <c r="F14" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="G14" t="n">
         <v>3.1828</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>5.1839</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9112</v>
       </c>
       <c r="F15" t="n">
+        <v>1.8597</v>
+      </c>
+      <c r="G15" t="n">
         <v>2.7259</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>5.1802</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9129</v>
       </c>
       <c r="F16" t="n">
+        <v>1.8563</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.715</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>5.17</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9356</v>
       </c>
       <c r="F17" t="n">
+        <v>1.8601</v>
+      </c>
+      <c r="G17" t="n">
         <v>2.3959</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>5.1812</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9651999999999999</v>
       </c>
       <c r="F18" t="n">
+        <v>1.6612</v>
+      </c>
+      <c r="G18" t="n">
         <v>1.9121</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>4.5428</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9688</v>
       </c>
       <c r="F19" t="n">
+        <v>1.7329</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.9149</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>4.783</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9603</v>
       </c>
       <c r="F20" t="n">
+        <v>1.7366</v>
+      </c>
+      <c r="G20" t="n">
         <v>2.0164</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4.795</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9560999999999999</v>
       </c>
       <c r="F21" t="n">
+        <v>1.7499</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.1601</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>4.838</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9577</v>
       </c>
       <c r="F22" t="n">
+        <v>1.746</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.1327</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>4.8253</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9535</v>
       </c>
       <c r="F23" t="n">
+        <v>1.7434</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.143</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>4.817</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.955</v>
       </c>
       <c r="F24" t="n">
+        <v>1.7489</v>
+      </c>
+      <c r="G24" t="n">
         <v>2.1542</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4.8349</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9546</v>
       </c>
       <c r="F25" t="n">
+        <v>1.7578</v>
+      </c>
+      <c r="G25" t="n">
         <v>2.148</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>4.8634</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9764</v>
       </c>
       <c r="F26" t="n">
+        <v>1.7056</v>
+      </c>
+      <c r="G26" t="n">
         <v>1.712</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>4.6928</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9507</v>
       </c>
       <c r="F27" t="n">
+        <v>1.6803</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.2122</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>4.6079</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9673</v>
       </c>
       <c r="F28" t="n">
+        <v>1.6871</v>
+      </c>
+      <c r="G28" t="n">
         <v>1.9087</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4.6311</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9756</v>
       </c>
       <c r="F29" t="n">
+        <v>1.7025</v>
+      </c>
+      <c r="G29" t="n">
         <v>1.7059</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4.6827</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9595</v>
       </c>
       <c r="F30" t="n">
+        <v>1.7331</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.1264</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>4.7834</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9713000000000001</v>
       </c>
       <c r="F31" t="n">
+        <v>1.7472</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.7847</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>4.8294</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9673</v>
       </c>
       <c r="F32" t="n">
+        <v>1.728</v>
+      </c>
+      <c r="G32" t="n">
         <v>1.9063</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>4.767</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9666</v>
       </c>
       <c r="F33" t="n">
+        <v>1.7097</v>
+      </c>
+      <c r="G33" t="n">
         <v>1.8954</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>4.7066</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9724</v>
       </c>
       <c r="F34" t="n">
+        <v>1.3788</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.608</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>3.4386</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9835</v>
       </c>
       <c r="F35" t="n">
+        <v>1.3538</v>
+      </c>
+      <c r="G35" t="n">
         <v>1.3256</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>3.3232</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9832</v>
       </c>
       <c r="F36" t="n">
+        <v>1.3503</v>
+      </c>
+      <c r="G36" t="n">
         <v>1.3227</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>3.3066</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9808</v>
       </c>
       <c r="F37" t="n">
+        <v>1.3616</v>
+      </c>
+      <c r="G37" t="n">
         <v>1.354</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>3.3595</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9809</v>
       </c>
       <c r="F38" t="n">
+        <v>1.3724</v>
+      </c>
+      <c r="G38" t="n">
         <v>1.385</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>3.4096</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.963</v>
       </c>
       <c r="F39" t="n">
+        <v>1.3543</v>
+      </c>
+      <c r="G39" t="n">
         <v>1.7171</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>3.3254</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.978</v>
       </c>
       <c r="F40" t="n">
+        <v>1.392</v>
+      </c>
+      <c r="G40" t="n">
         <v>1.4509</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>3.498</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9841</v>
       </c>
       <c r="F41" t="n">
+        <v>1.3538</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.3214</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>3.3233</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9871</v>
       </c>
       <c r="F42" t="n">
+        <v>1.3038</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.1369</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>3.0795</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.985</v>
       </c>
       <c r="F43" t="n">
+        <v>1.3062</v>
+      </c>
+      <c r="G43" t="n">
         <v>1.2408</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>3.0913</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F44" t="n">
+        <v>1.3413</v>
+      </c>
+      <c r="G44" t="n">
         <v>1.301</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>3.2639</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9839</v>
       </c>
       <c r="F45" t="n">
+        <v>1.3711</v>
+      </c>
+      <c r="G45" t="n">
         <v>1.2787</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>3.4033</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9649</v>
       </c>
       <c r="F46" t="n">
+        <v>1.3676</v>
+      </c>
+      <c r="G46" t="n">
         <v>1.7082</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>3.3873</v>
       </c>
     </row>
@@ -1784,6 +1924,9 @@
         <v>1.379</v>
       </c>
       <c r="G47" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="H47" t="n">
         <v>3.4396</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.98</v>
       </c>
       <c r="F48" t="n">
+        <v>1.5981</v>
+      </c>
+      <c r="G48" t="n">
         <v>1.6115</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>4.3208</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9757</v>
       </c>
       <c r="F49" t="n">
+        <v>1.3095</v>
+      </c>
+      <c r="G49" t="n">
         <v>1.504</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>3.1081</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9865</v>
       </c>
       <c r="F50" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.0588</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>2.644</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.9655</v>
       </c>
       <c r="F51" t="n">
+        <v>1.2858</v>
+      </c>
+      <c r="G51" t="n">
         <v>1.5504</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>2.9866</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.9655</v>
       </c>
       <c r="F52" t="n">
+        <v>1.2793</v>
+      </c>
+      <c r="G52" t="n">
         <v>1.5478</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>2.9527</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.9849</v>
       </c>
       <c r="F53" t="n">
+        <v>1.2116</v>
+      </c>
+      <c r="G53" t="n">
         <v>1.0649</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>2.5701</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.9829</v>
       </c>
       <c r="F54" t="n">
+        <v>1.2083</v>
+      </c>
+      <c r="G54" t="n">
         <v>1.1067</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>2.5496</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.9715</v>
       </c>
       <c r="F55" t="n">
+        <v>1.2457</v>
+      </c>
+      <c r="G55" t="n">
         <v>1.4097</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>2.769</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.985</v>
       </c>
       <c r="F56" t="n">
+        <v>1.2432</v>
+      </c>
+      <c r="G56" t="n">
         <v>1.0897</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>2.755</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9864000000000001</v>
       </c>
       <c r="F57" t="n">
+        <v>1.2381</v>
+      </c>
+      <c r="G57" t="n">
         <v>1.0121</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>2.7262</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F58" t="n">
+        <v>1.618</v>
+      </c>
+      <c r="G58" t="n">
         <v>1.6073</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>4.3922</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.9747</v>
       </c>
       <c r="F59" t="n">
+        <v>1.613</v>
+      </c>
+      <c r="G59" t="n">
         <v>1.6163</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>4.3742</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.9737</v>
       </c>
       <c r="F60" t="n">
+        <v>1.612</v>
+      </c>
+      <c r="G60" t="n">
         <v>1.6288</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>4.3705</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.9737</v>
       </c>
       <c r="F61" t="n">
+        <v>1.6152</v>
+      </c>
+      <c r="G61" t="n">
         <v>1.6455</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>4.3819</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.9797</v>
       </c>
       <c r="F62" t="n">
+        <v>1.2401</v>
+      </c>
+      <c r="G62" t="n">
         <v>1.206</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>2.7376</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.9677</v>
       </c>
       <c r="F63" t="n">
+        <v>1.2497</v>
+      </c>
+      <c r="G63" t="n">
         <v>1.485</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>2.7917</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.9667</v>
       </c>
       <c r="F64" t="n">
+        <v>1.2508</v>
+      </c>
+      <c r="G64" t="n">
         <v>1.5082</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>2.7982</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.9695</v>
       </c>
       <c r="F65" t="n">
+        <v>1.2426</v>
+      </c>
+      <c r="G65" t="n">
         <v>1.4576</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>2.752</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.9865</v>
       </c>
       <c r="F66" t="n">
+        <v>1.2388</v>
+      </c>
+      <c r="G66" t="n">
         <v>1.0715</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>2.73</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.9749</v>
       </c>
       <c r="F67" t="n">
+        <v>1.2368</v>
+      </c>
+      <c r="G67" t="n">
         <v>1.3549</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>2.7185</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.9757</v>
       </c>
       <c r="F68" t="n">
+        <v>1.2396</v>
+      </c>
+      <c r="G68" t="n">
         <v>1.3549</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>2.7346</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9714</v>
       </c>
       <c r="F69" t="n">
+        <v>1.6585</v>
+      </c>
+      <c r="G69" t="n">
         <v>1.8031</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>4.5337</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9699</v>
       </c>
       <c r="F70" t="n">
+        <v>1.6732</v>
+      </c>
+      <c r="G70" t="n">
         <v>1.8486</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>4.5839</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9778</v>
       </c>
       <c r="F71" t="n">
+        <v>1.6568</v>
+      </c>
+      <c r="G71" t="n">
         <v>1.7019</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>4.5278</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9679</v>
       </c>
       <c r="F72" t="n">
+        <v>1.6385</v>
+      </c>
+      <c r="G72" t="n">
         <v>1.8539</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>4.4641</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9839</v>
       </c>
       <c r="F73" t="n">
+        <v>1.4187</v>
+      </c>
+      <c r="G73" t="n">
         <v>1.3647</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>3.615</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9787</v>
       </c>
       <c r="F74" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="G74" t="n">
         <v>1.5152</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>3.8098</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.8844</v>
       </c>
       <c r="F75" t="n">
+        <v>1.8624</v>
+      </c>
+      <c r="G75" t="n">
         <v>2.9984</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>5.1883</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.8844</v>
       </c>
       <c r="F76" t="n">
+        <v>1.8624</v>
+      </c>
+      <c r="G76" t="n">
         <v>2.9984</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>5.1883</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.9656</v>
       </c>
       <c r="F77" t="n">
+        <v>1.6348</v>
+      </c>
+      <c r="G77" t="n">
         <v>1.846</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>4.4512</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.9639</v>
       </c>
       <c r="F78" t="n">
+        <v>1.6363</v>
+      </c>
+      <c r="G78" t="n">
         <v>1.8777</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>4.4567</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.9546</v>
       </c>
       <c r="F79" t="n">
+        <v>1.6328</v>
+      </c>
+      <c r="G79" t="n">
         <v>2.0696</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>4.4444</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.9639</v>
       </c>
       <c r="F80" t="n">
+        <v>1.6355</v>
+      </c>
+      <c r="G80" t="n">
         <v>1.8797</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>4.4538</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.97</v>
       </c>
       <c r="F81" t="n">
+        <v>1.2487</v>
+      </c>
+      <c r="G81" t="n">
         <v>1.4504</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>2.7859</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.9693000000000001</v>
       </c>
       <c r="F82" t="n">
+        <v>1.2502</v>
+      </c>
+      <c r="G82" t="n">
         <v>1.4603</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>2.7946</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.8873</v>
       </c>
       <c r="F83" t="n">
+        <v>1.8646</v>
+      </c>
+      <c r="G83" t="n">
         <v>2.9791</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>5.195</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.8863</v>
       </c>
       <c r="F84" t="n">
+        <v>1.8643</v>
+      </c>
+      <c r="G84" t="n">
         <v>2.9797</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>5.1939</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.8875</v>
       </c>
       <c r="F85" t="n">
+        <v>1.8673</v>
+      </c>
+      <c r="G85" t="n">
         <v>2.9799</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>5.2031</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9728</v>
       </c>
       <c r="F86" t="n">
+        <v>1.6709</v>
+      </c>
+      <c r="G86" t="n">
         <v>1.8328</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>4.5759</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9673</v>
       </c>
       <c r="F87" t="n">
+        <v>1.6815</v>
+      </c>
+      <c r="G87" t="n">
         <v>1.973</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>4.6122</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.974</v>
       </c>
       <c r="F88" t="n">
+        <v>1.6575</v>
+      </c>
+      <c r="G88" t="n">
         <v>1.8187</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>4.5301</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9648</v>
       </c>
       <c r="F89" t="n">
+        <v>1.6409</v>
+      </c>
+      <c r="G89" t="n">
         <v>1.8971</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>4.4727</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.985</v>
       </c>
       <c r="F90" t="n">
+        <v>1.3063</v>
+      </c>
+      <c r="G90" t="n">
         <v>1.2404</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>3.092</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9825</v>
       </c>
       <c r="F91" t="n">
+        <v>1.3413</v>
+      </c>
+      <c r="G91" t="n">
         <v>1.2984</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>3.2639</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.974</v>
       </c>
       <c r="F92" t="n">
+        <v>1.6575</v>
+      </c>
+      <c r="G92" t="n">
         <v>1.8187</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>4.5301</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9825</v>
       </c>
       <c r="F93" t="n">
+        <v>1.3413</v>
+      </c>
+      <c r="G93" t="n">
         <v>1.2984</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>3.2639</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9619</v>
       </c>
       <c r="F94" t="n">
+        <v>1.7763</v>
+      </c>
+      <c r="G94" t="n">
         <v>1.943</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>4.9225</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.8259</v>
       </c>
       <c r="F95" t="n">
+        <v>1.9189</v>
+      </c>
+      <c r="G95" t="n">
         <v>3.5474</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>5.3554</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9332</v>
       </c>
       <c r="F96" t="n">
+        <v>1.7752</v>
+      </c>
+      <c r="G96" t="n">
         <v>2.3877</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>4.9189</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9216</v>
       </c>
       <c r="F97" t="n">
+        <v>1.7742</v>
+      </c>
+      <c r="G97" t="n">
         <v>2.4825</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>4.9159</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9469</v>
       </c>
       <c r="F98" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="G98" t="n">
         <v>2.0304</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>3.9664</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9595</v>
       </c>
       <c r="F99" t="n">
+        <v>1.5102</v>
+      </c>
+      <c r="G99" t="n">
         <v>1.763</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>3.9908</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.956</v>
       </c>
       <c r="F100" t="n">
+        <v>1.5112</v>
+      </c>
+      <c r="G100" t="n">
         <v>1.8348</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>3.9943</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9708</v>
       </c>
       <c r="F101" t="n">
+        <v>1.5341</v>
+      </c>
+      <c r="G101" t="n">
         <v>1.5701</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>4.0831</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9582000000000001</v>
       </c>
       <c r="F102" t="n">
+        <v>1.5487</v>
+      </c>
+      <c r="G102" t="n">
         <v>1.8081</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>4.1386</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9506</v>
       </c>
       <c r="F103" t="n">
+        <v>1.5275</v>
+      </c>
+      <c r="G103" t="n">
         <v>1.9837</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>4.0577</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.944</v>
       </c>
       <c r="F104" t="n">
+        <v>1.5036</v>
+      </c>
+      <c r="G104" t="n">
         <v>2.0428</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>3.9648</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9395</v>
       </c>
       <c r="F105" t="n">
+        <v>1.5126</v>
+      </c>
+      <c r="G105" t="n">
         <v>2.0955</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9615</v>
       </c>
       <c r="F106" t="n">
+        <v>1.5167</v>
+      </c>
+      <c r="G106" t="n">
         <v>1.7467</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>4.0159</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9588</v>
       </c>
       <c r="F107" t="n">
+        <v>1.5262</v>
+      </c>
+      <c r="G107" t="n">
         <v>1.7934</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>4.0527</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9733000000000001</v>
       </c>
       <c r="F108" t="n">
+        <v>1.5011</v>
+      </c>
+      <c r="G108" t="n">
         <v>1.6148</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>3.9548</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F109" t="n">
+        <v>1.4859</v>
+      </c>
+      <c r="G109" t="n">
         <v>1.5684</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>3.8942</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.972</v>
       </c>
       <c r="F110" t="n">
+        <v>1.4971</v>
+      </c>
+      <c r="G110" t="n">
         <v>1.5976</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>3.9389</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.956</v>
       </c>
       <c r="F111" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="G111" t="n">
         <v>1.877</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>3.8139</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9789</v>
       </c>
       <c r="F112" t="n">
+        <v>1.4028</v>
+      </c>
+      <c r="G112" t="n">
         <v>1.4349</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>3.5458</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9792</v>
       </c>
       <c r="F113" t="n">
+        <v>1.4231</v>
+      </c>
+      <c r="G113" t="n">
         <v>1.3957</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>3.6341</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9724</v>
       </c>
       <c r="F114" t="n">
+        <v>1.4812</v>
+      </c>
+      <c r="G114" t="n">
         <v>1.5799</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>3.8757</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9562</v>
       </c>
       <c r="F115" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="G115" t="n">
         <v>1.871</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>3.8219</v>
       </c>
     </row>
@@ -3775,16 +4122,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
         <v>0.966</v>
       </c>
       <c r="F116" t="n">
+        <v>1.2527</v>
+      </c>
+      <c r="G116" t="n">
         <v>1.5298</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>2.8087</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.9789</v>
       </c>
       <c r="F117" t="n">
+        <v>1.2532</v>
+      </c>
+      <c r="G117" t="n">
         <v>1.2371</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>2.8115</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9395</v>
       </c>
       <c r="F118" t="n">
+        <v>1.5126</v>
+      </c>
+      <c r="G118" t="n">
         <v>2.0955</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9792</v>
       </c>
       <c r="F119" t="n">
+        <v>1.4231</v>
+      </c>
+      <c r="G119" t="n">
         <v>1.3957</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>3.6341</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9005</v>
       </c>
       <c r="F120" t="n">
+        <v>1.8044</v>
+      </c>
+      <c r="G120" t="n">
         <v>2.6965</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>5.0107</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9005</v>
       </c>
       <c r="F121" t="n">
+        <v>1.8044</v>
+      </c>
+      <c r="G121" t="n">
         <v>2.6965</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>5.0107</v>
       </c>
     </row>
@@ -3949,16 +4314,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>0.925</v>
       </c>
       <c r="F122" t="n">
-        <v>2.3774</v>
+        <v>1.6368</v>
       </c>
       <c r="G122" t="n">
+        <v>2.3772</v>
+      </c>
+      <c r="H122" t="n">
         <v>4.4583</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9791</v>
       </c>
       <c r="F123" t="n">
+        <v>1.4233</v>
+      </c>
+      <c r="G123" t="n">
         <v>1.3968</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>3.635</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9765</v>
       </c>
       <c r="F124" t="n">
+        <v>1.4321</v>
+      </c>
+      <c r="G124" t="n">
         <v>1.4713</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>3.6725</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9338</v>
       </c>
       <c r="F125" t="n">
+        <v>1.7774</v>
+      </c>
+      <c r="G125" t="n">
         <v>2.3725</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>4.926</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.8822</v>
       </c>
       <c r="F126" t="n">
+        <v>1.7996</v>
+      </c>
+      <c r="G126" t="n">
         <v>2.969</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>4.9958</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F127" t="n">
+        <v>1.3428</v>
+      </c>
+      <c r="G127" t="n">
         <v>1.3453</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>3.2713</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="F128" t="n">
+        <v>1.8077</v>
+      </c>
+      <c r="G128" t="n">
         <v>3.0644</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>5.0209</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.8826000000000001</v>
       </c>
       <c r="F129" t="n">
+        <v>1.8048</v>
+      </c>
+      <c r="G129" t="n">
         <v>2.9585</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>5.012</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.8818</v>
       </c>
       <c r="F130" t="n">
+        <v>1.8043</v>
+      </c>
+      <c r="G130" t="n">
         <v>2.9664</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>5.0105</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.8784</v>
       </c>
       <c r="F131" t="n">
+        <v>1.796</v>
+      </c>
+      <c r="G131" t="n">
         <v>2.9992</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>4.9844</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.8797</v>
       </c>
       <c r="F132" t="n">
+        <v>1.8079</v>
+      </c>
+      <c r="G132" t="n">
         <v>2.9788</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>5.0217</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.8746</v>
       </c>
       <c r="F133" t="n">
+        <v>1.8143</v>
+      </c>
+      <c r="G133" t="n">
         <v>3.068</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>5.0416</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.8843</v>
       </c>
       <c r="F134" t="n">
+        <v>1.8082</v>
+      </c>
+      <c r="G134" t="n">
         <v>2.9551</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>5.0227</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.8748</v>
       </c>
       <c r="F135" t="n">
+        <v>1.8076</v>
+      </c>
+      <c r="G135" t="n">
         <v>3.0649</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>5.0207</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.8786</v>
       </c>
       <c r="F136" t="n">
+        <v>1.7947</v>
+      </c>
+      <c r="G136" t="n">
         <v>2.9933</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>4.9803</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9645</v>
       </c>
       <c r="F137" t="n">
+        <v>1.7287</v>
+      </c>
+      <c r="G137" t="n">
         <v>1.9431</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>4.769</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9627</v>
       </c>
       <c r="F138" t="n">
+        <v>1.669</v>
+      </c>
+      <c r="G138" t="n">
         <v>1.9674</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>4.5695</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.952</v>
       </c>
       <c r="F139" t="n">
+        <v>1.7377</v>
+      </c>
+      <c r="G139" t="n">
         <v>2.1509</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>4.7985</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.971</v>
       </c>
       <c r="F140" t="n">
+        <v>1.3654</v>
+      </c>
+      <c r="G140" t="n">
         <v>1.6048</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>3.3773</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.985</v>
       </c>
       <c r="F141" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G141" t="n">
         <v>1.2809</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>3.4213</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9627</v>
       </c>
       <c r="F142" t="n">
+        <v>1.669</v>
+      </c>
+      <c r="G142" t="n">
         <v>1.9674</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>4.5695</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9346</v>
       </c>
       <c r="F143" t="n">
+        <v>1.7283</v>
+      </c>
+      <c r="G143" t="n">
         <v>2.423</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>4.7677</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9706</v>
       </c>
       <c r="F144" t="n">
+        <v>1.7197</v>
+      </c>
+      <c r="G144" t="n">
         <v>1.7568</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>4.7397</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.985</v>
       </c>
       <c r="F145" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G145" t="n">
         <v>1.2809</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>3.4213</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.9721</v>
       </c>
       <c r="F146" t="n">
+        <v>1.3388</v>
+      </c>
+      <c r="G146" t="n">
         <v>1.4527</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>3.2518</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.9826</v>
       </c>
       <c r="F147" t="n">
+        <v>1.3362</v>
+      </c>
+      <c r="G147" t="n">
         <v>1.1804</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>3.2395</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.9779</v>
       </c>
       <c r="F148" t="n">
+        <v>1.3398</v>
+      </c>
+      <c r="G148" t="n">
         <v>1.3279</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>3.2568</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.9772</v>
       </c>
       <c r="F149" t="n">
+        <v>1.3459</v>
+      </c>
+      <c r="G149" t="n">
         <v>1.3481</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>3.2857</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F150" t="n">
+        <v>1.3404</v>
+      </c>
+      <c r="G150" t="n">
         <v>1.3216</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>3.2596</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F151" t="n">
+        <v>1.3411</v>
+      </c>
+      <c r="G151" t="n">
         <v>1.3179</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>3.263</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.9836</v>
       </c>
       <c r="F152" t="n">
+        <v>1.3352</v>
+      </c>
+      <c r="G152" t="n">
         <v>1.1445</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>3.2344</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.9842</v>
       </c>
       <c r="F153" t="n">
+        <v>1.3379</v>
+      </c>
+      <c r="G153" t="n">
         <v>1.1358</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>3.2475</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.9741</v>
       </c>
       <c r="F154" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="G154" t="n">
         <v>1.4144</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>3.2529</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.9676</v>
       </c>
       <c r="F155" t="n">
+        <v>1.2553</v>
+      </c>
+      <c r="G155" t="n">
         <v>1.4842</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>2.8228</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.9853</v>
       </c>
       <c r="F156" t="n">
+        <v>1.2505</v>
+      </c>
+      <c r="G156" t="n">
         <v>1.0314</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>2.7964</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.9847</v>
       </c>
       <c r="F157" t="n">
+        <v>1.2463</v>
+      </c>
+      <c r="G157" t="n">
         <v>1.0346</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>2.7726</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.9757</v>
       </c>
       <c r="F158" t="n">
+        <v>1.2355</v>
+      </c>
+      <c r="G158" t="n">
         <v>1.3282</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>2.7111</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.8824</v>
       </c>
       <c r="F159" t="n">
+        <v>1.8155</v>
+      </c>
+      <c r="G159" t="n">
         <v>3.0298</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>5.0451</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.9752</v>
       </c>
       <c r="F160" t="n">
+        <v>1.4205</v>
+      </c>
+      <c r="G160" t="n">
         <v>1.5211</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>3.6229</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.9756</v>
       </c>
       <c r="F161" t="n">
+        <v>1.4196</v>
+      </c>
+      <c r="G161" t="n">
         <v>1.5019</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>3.6188</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.8917</v>
       </c>
       <c r="F162" t="n">
+        <v>1.8208</v>
+      </c>
+      <c r="G162" t="n">
         <v>2.8866</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>5.0614</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9722</v>
       </c>
       <c r="F163" t="n">
+        <v>1.6807</v>
+      </c>
+      <c r="G163" t="n">
         <v>1.8066</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>4.6095</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9708</v>
       </c>
       <c r="F164" t="n">
+        <v>1.3655</v>
+      </c>
+      <c r="G164" t="n">
         <v>1.6055</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>3.3775</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9338</v>
       </c>
       <c r="F165" t="n">
+        <v>1.7774</v>
+      </c>
+      <c r="G165" t="n">
         <v>2.3725</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>4.926</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.9615</v>
       </c>
       <c r="F166" t="n">
+        <v>1.9217</v>
+      </c>
+      <c r="G166" t="n">
         <v>2.1027</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>5.3637</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F167" t="n">
+        <v>1.6665</v>
+      </c>
+      <c r="G167" t="n">
         <v>1.7323</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>4.561</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9731</v>
       </c>
       <c r="F168" t="n">
+        <v>1.3418</v>
+      </c>
+      <c r="G168" t="n">
         <v>1.5537</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>3.2664</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9853</v>
       </c>
       <c r="F169" t="n">
+        <v>1.2347</v>
+      </c>
+      <c r="G169" t="n">
         <v>1.0888</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>2.7066</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.971</v>
       </c>
       <c r="F170" t="n">
+        <v>1.4716</v>
+      </c>
+      <c r="G170" t="n">
         <v>1.8154</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>3.8368</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9812</v>
       </c>
       <c r="F171" t="n">
+        <v>1.3002</v>
+      </c>
+      <c r="G171" t="n">
         <v>1.2732</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>3.0612</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9645</v>
       </c>
       <c r="F172" t="n">
+        <v>1.7097</v>
+      </c>
+      <c r="G172" t="n">
         <v>1.9133</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>4.7066</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9849</v>
+        <v>0.9731</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2258</v>
+        <v>0.7451</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0816</v>
+        <v>1.4253</v>
       </c>
       <c r="H2" t="n">
-        <v>2.655</v>
+        <v>2.8128</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.98</v>
+        <v>0.9882</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2293</v>
+        <v>0.7291</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2587</v>
+        <v>1.0567</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6755</v>
+        <v>2.8998</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9619</v>
+        <v>0.8736</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7763</v>
+        <v>0.1597</v>
       </c>
       <c r="G4" t="n">
-        <v>1.943</v>
+        <v>3.0103</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9225</v>
+        <v>5.1067</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9734</v>
+        <v>0.9633</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6097</v>
+        <v>0.3715</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6337</v>
+        <v>1.8388</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3624</v>
+        <v>4.4164</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9749</v>
+        <v>0.9755</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6135</v>
+        <v>0.3909</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6027</v>
+        <v>1.6022</v>
       </c>
       <c r="H6" t="n">
-        <v>4.376</v>
+        <v>4.3478</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9452</v>
+        <v>0.8776</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8498</v>
+        <v>0.2649</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3034</v>
+        <v>3.0198</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1503</v>
+        <v>4.7764</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8623</v>
+        <v>0.2393</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2896</v>
+        <v>2.262</v>
       </c>
       <c r="H8" t="n">
-        <v>5.188</v>
+        <v>4.8588</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9825</v>
+        <v>0.973</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2729</v>
+        <v>0.669</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2608</v>
+        <v>1.519</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9185</v>
+        <v>3.2051</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8504</v>
+        <v>0.9643</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8608</v>
+        <v>0.2354</v>
       </c>
       <c r="G10" t="n">
-        <v>3.294</v>
+        <v>1.8778</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1835</v>
+        <v>4.8713</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.9443</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8602</v>
+        <v>0.2385</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1892</v>
+        <v>2.2614</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1816</v>
+        <v>4.8615</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8482</v>
+        <v>0.9647</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8608</v>
+        <v>0.2368</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3086</v>
+        <v>1.879</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1834</v>
+        <v>4.8666</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8492</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.863</v>
+        <v>0.2351</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2992</v>
+        <v>2.2715</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1901</v>
+        <v>4.8723</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8632</v>
+        <v>0.9442</v>
       </c>
       <c r="F14" t="n">
-        <v>1.861</v>
+        <v>0.2373</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1828</v>
+        <v>2.2603</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1839</v>
+        <v>4.8652</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9112</v>
+        <v>0.9443</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8597</v>
+        <v>0.2369</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7259</v>
+        <v>2.2606</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1802</v>
+        <v>4.8665</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9129</v>
+        <v>0.9436</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8563</v>
+        <v>0.2322</v>
       </c>
       <c r="G16" t="n">
-        <v>2.715</v>
+        <v>2.2614</v>
       </c>
       <c r="H16" t="n">
-        <v>5.17</v>
+        <v>4.8813</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9356</v>
+        <v>0.9647</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8601</v>
+        <v>0.2332</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3959</v>
+        <v>1.8849</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1812</v>
+        <v>4.8783</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9707</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6612</v>
+        <v>0.3619</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9121</v>
+        <v>1.8121</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5428</v>
+        <v>4.4499</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9688</v>
+        <v>0.9637</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7329</v>
+        <v>0.3188</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9149</v>
+        <v>2.0611</v>
       </c>
       <c r="H19" t="n">
-        <v>4.783</v>
+        <v>4.5979</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9603</v>
+        <v>0.9741</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7366</v>
+        <v>0.313</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0164</v>
+        <v>1.7666</v>
       </c>
       <c r="H20" t="n">
-        <v>4.795</v>
+        <v>4.6174</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.975</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7499</v>
+        <v>0.3135</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1601</v>
+        <v>1.756</v>
       </c>
       <c r="H21" t="n">
-        <v>4.838</v>
+        <v>4.6159</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9577</v>
+        <v>0.9674</v>
       </c>
       <c r="F22" t="n">
-        <v>1.746</v>
+        <v>0.3194</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1327</v>
+        <v>1.8895</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8253</v>
+        <v>4.5959</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9535</v>
+        <v>0.9746</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7434</v>
+        <v>0.3166</v>
       </c>
       <c r="G23" t="n">
-        <v>2.143</v>
+        <v>1.6974</v>
       </c>
       <c r="H23" t="n">
-        <v>4.817</v>
+        <v>4.6052</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.955</v>
+        <v>0.9562</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7489</v>
+        <v>0.2909</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1542</v>
+        <v>2.1227</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8349</v>
+        <v>4.691</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9546</v>
+        <v>0.9721</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7578</v>
+        <v>0.2919</v>
       </c>
       <c r="G25" t="n">
-        <v>2.148</v>
+        <v>1.7896</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8634</v>
+        <v>4.6879</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9764</v>
+        <v>0.9722</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7056</v>
+        <v>0.3308</v>
       </c>
       <c r="G26" t="n">
-        <v>1.712</v>
+        <v>1.837</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6928</v>
+        <v>4.5572</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9507</v>
+        <v>0.9722</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6803</v>
+        <v>0.3543</v>
       </c>
       <c r="G27" t="n">
-        <v>2.2122</v>
+        <v>1.796</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6079</v>
+        <v>4.4764</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9673</v>
+        <v>0.972</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6871</v>
+        <v>0.3332</v>
       </c>
       <c r="G28" t="n">
-        <v>1.9087</v>
+        <v>1.818</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6311</v>
+        <v>4.5491</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9756</v>
+        <v>0.9718</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7025</v>
+        <v>0.3179</v>
       </c>
       <c r="G29" t="n">
-        <v>1.7059</v>
+        <v>1.85</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6827</v>
+        <v>4.6008</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9595</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7331</v>
+        <v>0.3169</v>
       </c>
       <c r="G30" t="n">
-        <v>2.1264</v>
+        <v>1.6897</v>
       </c>
       <c r="H30" t="n">
-        <v>4.7834</v>
+        <v>4.6043</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9746</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7472</v>
+        <v>0.318</v>
       </c>
       <c r="G31" t="n">
-        <v>1.7847</v>
+        <v>1.7462</v>
       </c>
       <c r="H31" t="n">
-        <v>4.8294</v>
+        <v>4.6006</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9673</v>
+        <v>0.9614</v>
       </c>
       <c r="F32" t="n">
-        <v>1.728</v>
+        <v>0.3281</v>
       </c>
       <c r="G32" t="n">
-        <v>1.9063</v>
+        <v>1.9917</v>
       </c>
       <c r="H32" t="n">
-        <v>4.767</v>
+        <v>4.5664</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9666</v>
+        <v>0.9701</v>
       </c>
       <c r="F33" t="n">
-        <v>1.7097</v>
+        <v>0.3392</v>
       </c>
       <c r="G33" t="n">
-        <v>1.8954</v>
+        <v>1.8195</v>
       </c>
       <c r="H33" t="n">
-        <v>4.7066</v>
+        <v>4.5287</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9724</v>
+        <v>0.971</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3788</v>
+        <v>0.5836</v>
       </c>
       <c r="G34" t="n">
-        <v>1.608</v>
+        <v>1.6649</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4386</v>
+        <v>3.5947</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9835</v>
+        <v>0.9869</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3538</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>1.3256</v>
+        <v>1.2702</v>
       </c>
       <c r="H35" t="n">
-        <v>3.3232</v>
+        <v>3.5573</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9832</v>
+        <v>0.9806</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3503</v>
+        <v>0.606</v>
       </c>
       <c r="G36" t="n">
-        <v>1.3227</v>
+        <v>1.4403</v>
       </c>
       <c r="H36" t="n">
-        <v>3.3066</v>
+        <v>3.4968</v>
       </c>
     </row>
     <row r="37">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9808</v>
+        <v>0.9799</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3616</v>
+        <v>0.6319</v>
       </c>
       <c r="G37" t="n">
-        <v>1.354</v>
+        <v>1.3637</v>
       </c>
       <c r="H37" t="n">
-        <v>3.3595</v>
+        <v>3.3798</v>
       </c>
     </row>
     <row r="38">
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9809</v>
+        <v>0.9807</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3724</v>
+        <v>0.5961</v>
       </c>
       <c r="G38" t="n">
-        <v>1.385</v>
+        <v>1.4016</v>
       </c>
       <c r="H38" t="n">
-        <v>3.4096</v>
+        <v>3.5405</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.963</v>
+        <v>0.9664</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3543</v>
+        <v>0.6327</v>
       </c>
       <c r="G39" t="n">
-        <v>1.7171</v>
+        <v>1.6858</v>
       </c>
       <c r="H39" t="n">
-        <v>3.3254</v>
+        <v>3.3762</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.978</v>
+        <v>0.982</v>
       </c>
       <c r="F40" t="n">
-        <v>1.392</v>
+        <v>0.5735</v>
       </c>
       <c r="G40" t="n">
-        <v>1.4509</v>
+        <v>1.333</v>
       </c>
       <c r="H40" t="n">
-        <v>3.498</v>
+        <v>3.6383</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9841</v>
+        <v>0.9727</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3538</v>
+        <v>0.5889</v>
       </c>
       <c r="G41" t="n">
-        <v>1.3214</v>
+        <v>1.6353</v>
       </c>
       <c r="H41" t="n">
-        <v>3.3233</v>
+        <v>3.5717</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9871</v>
+        <v>0.9717</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3038</v>
+        <v>0.6456</v>
       </c>
       <c r="G42" t="n">
-        <v>1.1369</v>
+        <v>1.5797</v>
       </c>
       <c r="H42" t="n">
-        <v>3.0795</v>
+        <v>3.3166</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.985</v>
+        <v>0.9866</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3062</v>
+        <v>0.6434</v>
       </c>
       <c r="G43" t="n">
-        <v>1.2408</v>
+        <v>1.2619</v>
       </c>
       <c r="H43" t="n">
-        <v>3.0913</v>
+        <v>3.3268</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9873</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3413</v>
+        <v>0.6428</v>
       </c>
       <c r="G44" t="n">
-        <v>1.301</v>
+        <v>1.1825</v>
       </c>
       <c r="H44" t="n">
-        <v>3.2639</v>
+        <v>3.3297</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9839</v>
+        <v>0.9807</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3711</v>
+        <v>0.5971</v>
       </c>
       <c r="G45" t="n">
-        <v>1.2787</v>
+        <v>1.4033</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4033</v>
+        <v>3.5359</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9649</v>
+        <v>0.968</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3676</v>
+        <v>0.6248</v>
       </c>
       <c r="G46" t="n">
-        <v>1.7082</v>
+        <v>1.6986</v>
       </c>
       <c r="H46" t="n">
-        <v>3.3873</v>
+        <v>3.4124</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9804</v>
+        <v>0.9825</v>
       </c>
       <c r="F47" t="n">
-        <v>1.379</v>
+        <v>0.5792</v>
       </c>
       <c r="G47" t="n">
-        <v>1.379</v>
+        <v>1.3369</v>
       </c>
       <c r="H47" t="n">
-        <v>3.4396</v>
+        <v>3.6136</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.98</v>
+        <v>0.9717</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5981</v>
+        <v>0.3885</v>
       </c>
       <c r="G48" t="n">
-        <v>1.6115</v>
+        <v>1.9355</v>
       </c>
       <c r="H48" t="n">
-        <v>4.3208</v>
+        <v>4.3564</v>
       </c>
     </row>
     <row r="49">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9757</v>
+        <v>0.975</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3095</v>
+        <v>0.6449</v>
       </c>
       <c r="G49" t="n">
-        <v>1.504</v>
+        <v>1.5463</v>
       </c>
       <c r="H49" t="n">
-        <v>3.1081</v>
+        <v>3.3199</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9865</v>
+        <v>0.9863</v>
       </c>
       <c r="F50" t="n">
-        <v>1.224</v>
+        <v>0.7501</v>
       </c>
       <c r="G50" t="n">
-        <v>1.0588</v>
+        <v>1.0844</v>
       </c>
       <c r="H50" t="n">
-        <v>2.644</v>
+        <v>2.7851</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9655</v>
+        <v>0.9791</v>
       </c>
       <c r="F51" t="n">
-        <v>1.2858</v>
+        <v>0.7047</v>
       </c>
       <c r="G51" t="n">
-        <v>1.5504</v>
+        <v>1.2553</v>
       </c>
       <c r="H51" t="n">
-        <v>2.9866</v>
+        <v>3.0273</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9655</v>
+        <v>0.9637</v>
       </c>
       <c r="F52" t="n">
-        <v>1.2793</v>
+        <v>0.7221</v>
       </c>
       <c r="G52" t="n">
-        <v>1.5478</v>
+        <v>1.5885</v>
       </c>
       <c r="H52" t="n">
-        <v>2.9527</v>
+        <v>2.9366</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9849</v>
+        <v>0.9839</v>
       </c>
       <c r="F53" t="n">
-        <v>1.2116</v>
+        <v>0.7608</v>
       </c>
       <c r="G53" t="n">
-        <v>1.0649</v>
+        <v>1.1061</v>
       </c>
       <c r="H53" t="n">
-        <v>2.5701</v>
+        <v>2.7246</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9829</v>
+        <v>0.9839</v>
       </c>
       <c r="F54" t="n">
-        <v>1.2083</v>
+        <v>0.7688</v>
       </c>
       <c r="G54" t="n">
-        <v>1.1067</v>
+        <v>1.0936</v>
       </c>
       <c r="H54" t="n">
-        <v>2.5496</v>
+        <v>2.6784</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9715</v>
+        <v>0.9822</v>
       </c>
       <c r="F55" t="n">
-        <v>1.2457</v>
+        <v>0.7277</v>
       </c>
       <c r="G55" t="n">
-        <v>1.4097</v>
+        <v>1.164</v>
       </c>
       <c r="H55" t="n">
-        <v>2.769</v>
+        <v>2.907</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.985</v>
+        <v>0.9832</v>
       </c>
       <c r="F56" t="n">
-        <v>1.2432</v>
+        <v>0.7392</v>
       </c>
       <c r="G56" t="n">
-        <v>1.0897</v>
+        <v>1.1428</v>
       </c>
       <c r="H56" t="n">
-        <v>2.755</v>
+        <v>2.845</v>
       </c>
     </row>
     <row r="57">
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9869</v>
       </c>
       <c r="F57" t="n">
-        <v>1.2381</v>
+        <v>0.7613</v>
       </c>
       <c r="G57" t="n">
-        <v>1.0121</v>
+        <v>1.0544</v>
       </c>
       <c r="H57" t="n">
-        <v>2.7262</v>
+        <v>2.7215</v>
       </c>
     </row>
     <row r="58">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9745</v>
       </c>
       <c r="F58" t="n">
-        <v>1.618</v>
+        <v>0.3885</v>
       </c>
       <c r="G58" t="n">
-        <v>1.6073</v>
+        <v>1.6197</v>
       </c>
       <c r="H58" t="n">
-        <v>4.3922</v>
+        <v>4.3564</v>
       </c>
     </row>
     <row r="59">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9747</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>1.613</v>
+        <v>0.3893</v>
       </c>
       <c r="G59" t="n">
-        <v>1.6163</v>
+        <v>1.6345</v>
       </c>
       <c r="H59" t="n">
-        <v>4.3742</v>
+        <v>4.3535</v>
       </c>
     </row>
     <row r="60">
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9737</v>
+        <v>0.9751</v>
       </c>
       <c r="F60" t="n">
-        <v>1.612</v>
+        <v>0.3931</v>
       </c>
       <c r="G60" t="n">
-        <v>1.6288</v>
+        <v>1.6121</v>
       </c>
       <c r="H60" t="n">
-        <v>4.3705</v>
+        <v>4.3398</v>
       </c>
     </row>
     <row r="61">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9737</v>
+        <v>0.9746</v>
       </c>
       <c r="F61" t="n">
-        <v>1.6152</v>
+        <v>0.3959</v>
       </c>
       <c r="G61" t="n">
-        <v>1.6455</v>
+        <v>1.6159</v>
       </c>
       <c r="H61" t="n">
-        <v>4.3819</v>
+        <v>4.3299</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9797</v>
+        <v>0.9822</v>
       </c>
       <c r="F62" t="n">
-        <v>1.2401</v>
+        <v>0.742</v>
       </c>
       <c r="G62" t="n">
-        <v>1.206</v>
+        <v>1.1573</v>
       </c>
       <c r="H62" t="n">
-        <v>2.7376</v>
+        <v>2.8299</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9677</v>
+        <v>0.9805</v>
       </c>
       <c r="F63" t="n">
-        <v>1.2497</v>
+        <v>0.7399</v>
       </c>
       <c r="G63" t="n">
-        <v>1.485</v>
+        <v>1.1981</v>
       </c>
       <c r="H63" t="n">
-        <v>2.7917</v>
+        <v>2.8411</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9667</v>
+        <v>0.9654</v>
       </c>
       <c r="F64" t="n">
-        <v>1.2508</v>
+        <v>0.7331</v>
       </c>
       <c r="G64" t="n">
-        <v>1.5082</v>
+        <v>1.5361</v>
       </c>
       <c r="H64" t="n">
-        <v>2.7982</v>
+        <v>2.878</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9695</v>
+        <v>0.9658</v>
       </c>
       <c r="F65" t="n">
-        <v>1.2426</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>1.4576</v>
+        <v>1.5466</v>
       </c>
       <c r="H65" t="n">
-        <v>2.752</v>
+        <v>2.871</v>
       </c>
     </row>
     <row r="66">
@@ -2526,16 +2526,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9865</v>
+        <v>0.9845</v>
       </c>
       <c r="F66" t="n">
-        <v>1.2388</v>
+        <v>0.7642</v>
       </c>
       <c r="G66" t="n">
-        <v>1.0715</v>
+        <v>1.1174</v>
       </c>
       <c r="H66" t="n">
-        <v>2.73</v>
+        <v>2.7049</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9749</v>
+        <v>0.9736</v>
       </c>
       <c r="F67" t="n">
-        <v>1.2368</v>
+        <v>0.7556</v>
       </c>
       <c r="G67" t="n">
-        <v>1.3549</v>
+        <v>1.3974</v>
       </c>
       <c r="H67" t="n">
-        <v>2.7185</v>
+        <v>2.754</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9757</v>
+        <v>0.9764</v>
       </c>
       <c r="F68" t="n">
-        <v>1.2396</v>
+        <v>0.7599</v>
       </c>
       <c r="G68" t="n">
-        <v>1.3549</v>
+        <v>1.3618</v>
       </c>
       <c r="H68" t="n">
-        <v>2.7346</v>
+        <v>2.7295</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9714</v>
+        <v>0.9463</v>
       </c>
       <c r="F69" t="n">
-        <v>1.6585</v>
+        <v>0.352</v>
       </c>
       <c r="G69" t="n">
-        <v>1.8031</v>
+        <v>2.2855</v>
       </c>
       <c r="H69" t="n">
-        <v>4.5337</v>
+        <v>4.4843</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9699</v>
+        <v>0.9429</v>
       </c>
       <c r="F70" t="n">
-        <v>1.6732</v>
+        <v>0.3484</v>
       </c>
       <c r="G70" t="n">
-        <v>1.8486</v>
+        <v>2.312</v>
       </c>
       <c r="H70" t="n">
-        <v>4.5839</v>
+        <v>4.4969</v>
       </c>
     </row>
     <row r="71">
@@ -2686,16 +2686,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9778</v>
+        <v>0.9796</v>
       </c>
       <c r="F71" t="n">
-        <v>1.6568</v>
+        <v>0.3387</v>
       </c>
       <c r="G71" t="n">
-        <v>1.7019</v>
+        <v>1.6776</v>
       </c>
       <c r="H71" t="n">
-        <v>4.5278</v>
+        <v>4.5302</v>
       </c>
     </row>
     <row r="72">
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9679</v>
+        <v>0.9727</v>
       </c>
       <c r="F72" t="n">
-        <v>1.6385</v>
+        <v>0.369</v>
       </c>
       <c r="G72" t="n">
-        <v>1.8539</v>
+        <v>1.8605</v>
       </c>
       <c r="H72" t="n">
-        <v>4.4641</v>
+        <v>4.4252</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9839</v>
+        <v>0.981</v>
       </c>
       <c r="F73" t="n">
-        <v>1.4187</v>
+        <v>0.5159</v>
       </c>
       <c r="G73" t="n">
-        <v>1.3647</v>
+        <v>1.4712</v>
       </c>
       <c r="H73" t="n">
-        <v>3.615</v>
+        <v>3.8761</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9787</v>
+        <v>0.9782</v>
       </c>
       <c r="F74" t="n">
-        <v>1.465</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>1.5152</v>
+        <v>1.5434</v>
       </c>
       <c r="H74" t="n">
-        <v>3.8098</v>
+        <v>3.8165</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.8844</v>
+        <v>0.9443</v>
       </c>
       <c r="F75" t="n">
-        <v>1.8624</v>
+        <v>0.2574</v>
       </c>
       <c r="G75" t="n">
-        <v>2.9984</v>
+        <v>2.2731</v>
       </c>
       <c r="H75" t="n">
-        <v>5.1883</v>
+        <v>4.8007</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8844</v>
+        <v>0.9443</v>
       </c>
       <c r="F76" t="n">
-        <v>1.8624</v>
+        <v>0.2574</v>
       </c>
       <c r="G76" t="n">
-        <v>2.9984</v>
+        <v>2.2731</v>
       </c>
       <c r="H76" t="n">
-        <v>5.1883</v>
+        <v>4.8007</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9656</v>
+        <v>0.9627</v>
       </c>
       <c r="F77" t="n">
-        <v>1.6348</v>
+        <v>0.3633</v>
       </c>
       <c r="G77" t="n">
-        <v>1.846</v>
+        <v>1.8626</v>
       </c>
       <c r="H77" t="n">
-        <v>4.4512</v>
+        <v>4.4452</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9639</v>
+        <v>0.9627</v>
       </c>
       <c r="F78" t="n">
-        <v>1.6363</v>
+        <v>0.3517</v>
       </c>
       <c r="G78" t="n">
-        <v>1.8777</v>
+        <v>1.871</v>
       </c>
       <c r="H78" t="n">
-        <v>4.4567</v>
+        <v>4.4856</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9546</v>
+        <v>0.962</v>
       </c>
       <c r="F79" t="n">
-        <v>1.6328</v>
+        <v>0.3459</v>
       </c>
       <c r="G79" t="n">
-        <v>2.0696</v>
+        <v>1.8886</v>
       </c>
       <c r="H79" t="n">
-        <v>4.4444</v>
+        <v>4.5057</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9639</v>
+        <v>0.9626</v>
       </c>
       <c r="F80" t="n">
-        <v>1.6355</v>
+        <v>0.3533</v>
       </c>
       <c r="G80" t="n">
-        <v>1.8797</v>
+        <v>1.8707</v>
       </c>
       <c r="H80" t="n">
-        <v>4.4538</v>
+        <v>4.4801</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.97</v>
+        <v>0.9847</v>
       </c>
       <c r="F81" t="n">
-        <v>1.2487</v>
+        <v>0.7461</v>
       </c>
       <c r="G81" t="n">
-        <v>1.4504</v>
+        <v>1.0779</v>
       </c>
       <c r="H81" t="n">
-        <v>2.7859</v>
+        <v>2.8071</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9679</v>
       </c>
       <c r="F82" t="n">
-        <v>1.2502</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>1.4603</v>
+        <v>1.4997</v>
       </c>
       <c r="H82" t="n">
-        <v>2.7946</v>
+        <v>2.7995</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8873</v>
+        <v>0.9447</v>
       </c>
       <c r="F83" t="n">
-        <v>1.8646</v>
+        <v>0.2535</v>
       </c>
       <c r="G83" t="n">
-        <v>2.9791</v>
+        <v>2.2683</v>
       </c>
       <c r="H83" t="n">
-        <v>5.195</v>
+        <v>4.8133</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8863</v>
+        <v>0.9442</v>
       </c>
       <c r="F84" t="n">
-        <v>1.8643</v>
+        <v>0.251</v>
       </c>
       <c r="G84" t="n">
-        <v>2.9797</v>
+        <v>2.2705</v>
       </c>
       <c r="H84" t="n">
-        <v>5.1939</v>
+        <v>4.8214</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8875</v>
+        <v>0.9445</v>
       </c>
       <c r="F85" t="n">
-        <v>1.8673</v>
+        <v>0.2536</v>
       </c>
       <c r="G85" t="n">
-        <v>2.9799</v>
+        <v>2.2665</v>
       </c>
       <c r="H85" t="n">
-        <v>5.2031</v>
+        <v>4.8128</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9728</v>
+        <v>0.9528</v>
       </c>
       <c r="F86" t="n">
-        <v>1.6709</v>
+        <v>0.3265</v>
       </c>
       <c r="G86" t="n">
-        <v>1.8328</v>
+        <v>2.2117</v>
       </c>
       <c r="H86" t="n">
-        <v>4.5759</v>
+        <v>4.5718</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9673</v>
+        <v>0.9779</v>
       </c>
       <c r="F87" t="n">
-        <v>1.6815</v>
+        <v>0.3087</v>
       </c>
       <c r="G87" t="n">
-        <v>1.973</v>
+        <v>1.7618</v>
       </c>
       <c r="H87" t="n">
-        <v>4.6122</v>
+        <v>4.6319</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.974</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>1.6575</v>
+        <v>0.347</v>
       </c>
       <c r="G88" t="n">
-        <v>1.8187</v>
+        <v>2.2382</v>
       </c>
       <c r="H88" t="n">
-        <v>4.5301</v>
+        <v>4.5018</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9648</v>
+        <v>0.976</v>
       </c>
       <c r="F89" t="n">
-        <v>1.6409</v>
+        <v>0.354</v>
       </c>
       <c r="G89" t="n">
-        <v>1.8971</v>
+        <v>1.7724</v>
       </c>
       <c r="H89" t="n">
-        <v>4.4727</v>
+        <v>4.4777</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.985</v>
+        <v>0.9866</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3063</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>1.2404</v>
+        <v>1.2621</v>
       </c>
       <c r="H90" t="n">
-        <v>3.092</v>
+        <v>3.3258</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9825</v>
+        <v>0.9872</v>
       </c>
       <c r="F91" t="n">
-        <v>1.3413</v>
+        <v>0.6438</v>
       </c>
       <c r="G91" t="n">
-        <v>1.2984</v>
+        <v>1.1851</v>
       </c>
       <c r="H91" t="n">
-        <v>3.2639</v>
+        <v>3.3247</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.974</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>1.6575</v>
+        <v>0.347</v>
       </c>
       <c r="G92" t="n">
-        <v>1.8187</v>
+        <v>2.2382</v>
       </c>
       <c r="H92" t="n">
-        <v>4.5301</v>
+        <v>4.5018</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9825</v>
+        <v>0.9872</v>
       </c>
       <c r="F93" t="n">
-        <v>1.3413</v>
+        <v>0.6438</v>
       </c>
       <c r="G93" t="n">
-        <v>1.2984</v>
+        <v>1.1851</v>
       </c>
       <c r="H93" t="n">
-        <v>3.2639</v>
+        <v>3.3247</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9619</v>
+        <v>0.8736</v>
       </c>
       <c r="F94" t="n">
-        <v>1.7763</v>
+        <v>0.1597</v>
       </c>
       <c r="G94" t="n">
-        <v>1.943</v>
+        <v>3.0103</v>
       </c>
       <c r="H94" t="n">
-        <v>4.9225</v>
+        <v>5.1067</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8259</v>
+        <v>0.8175</v>
       </c>
       <c r="F95" t="n">
-        <v>1.9189</v>
+        <v>0.0472</v>
       </c>
       <c r="G95" t="n">
-        <v>3.5474</v>
+        <v>3.7131</v>
       </c>
       <c r="H95" t="n">
-        <v>5.3554</v>
+        <v>5.4378</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9332</v>
+        <v>0.8746</v>
       </c>
       <c r="F96" t="n">
-        <v>1.7752</v>
+        <v>0.1616</v>
       </c>
       <c r="G96" t="n">
-        <v>2.3877</v>
+        <v>3.0081</v>
       </c>
       <c r="H96" t="n">
-        <v>4.9189</v>
+        <v>5.1009</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9216</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>1.7742</v>
+        <v>0.1579</v>
       </c>
       <c r="G97" t="n">
-        <v>2.4825</v>
+        <v>2.3408</v>
       </c>
       <c r="H97" t="n">
-        <v>4.9159</v>
+        <v>5.1123</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9469</v>
+        <v>0.9505</v>
       </c>
       <c r="F98" t="n">
-        <v>1.504</v>
+        <v>0.4711</v>
       </c>
       <c r="G98" t="n">
-        <v>2.0304</v>
+        <v>1.9688</v>
       </c>
       <c r="H98" t="n">
-        <v>3.9664</v>
+        <v>4.0513</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9595</v>
+        <v>0.946</v>
       </c>
       <c r="F99" t="n">
-        <v>1.5102</v>
+        <v>0.4699</v>
       </c>
       <c r="G99" t="n">
-        <v>1.763</v>
+        <v>2.0402</v>
       </c>
       <c r="H99" t="n">
-        <v>3.9908</v>
+        <v>4.0559</v>
       </c>
     </row>
     <row r="100">
@@ -3614,16 +3614,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.956</v>
+        <v>0.9638</v>
       </c>
       <c r="F100" t="n">
-        <v>1.5112</v>
+        <v>0.4659</v>
       </c>
       <c r="G100" t="n">
-        <v>1.8348</v>
+        <v>1.7699</v>
       </c>
       <c r="H100" t="n">
-        <v>3.9943</v>
+        <v>4.0712</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9708</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>1.5341</v>
+        <v>0.4666</v>
       </c>
       <c r="G101" t="n">
-        <v>1.5701</v>
+        <v>1.8023</v>
       </c>
       <c r="H101" t="n">
-        <v>4.0831</v>
+        <v>4.0687</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9295</v>
       </c>
       <c r="F102" t="n">
-        <v>1.5487</v>
+        <v>0.4438</v>
       </c>
       <c r="G102" t="n">
-        <v>1.8081</v>
+        <v>2.239</v>
       </c>
       <c r="H102" t="n">
-        <v>4.1386</v>
+        <v>4.1546</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9506</v>
+        <v>0.9771</v>
       </c>
       <c r="F103" t="n">
-        <v>1.5275</v>
+        <v>0.4769</v>
       </c>
       <c r="G103" t="n">
-        <v>1.9837</v>
+        <v>1.4531</v>
       </c>
       <c r="H103" t="n">
-        <v>4.0577</v>
+        <v>4.029</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.944</v>
+        <v>0.9666</v>
       </c>
       <c r="F104" t="n">
-        <v>1.5036</v>
+        <v>0.4799</v>
       </c>
       <c r="G104" t="n">
-        <v>2.0428</v>
+        <v>1.6581</v>
       </c>
       <c r="H104" t="n">
-        <v>3.9648</v>
+        <v>4.0174</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9395</v>
+        <v>0.9651</v>
       </c>
       <c r="F105" t="n">
-        <v>1.5126</v>
+        <v>0.477</v>
       </c>
       <c r="G105" t="n">
-        <v>2.0955</v>
+        <v>1.6913</v>
       </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>4.0289</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9615</v>
+        <v>0.9425</v>
       </c>
       <c r="F106" t="n">
-        <v>1.5167</v>
+        <v>0.47</v>
       </c>
       <c r="G106" t="n">
-        <v>1.7467</v>
+        <v>2.0721</v>
       </c>
       <c r="H106" t="n">
-        <v>4.0159</v>
+        <v>4.0555</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9588</v>
+        <v>0.9749</v>
       </c>
       <c r="F107" t="n">
-        <v>1.5262</v>
+        <v>0.4648</v>
       </c>
       <c r="G107" t="n">
-        <v>1.7934</v>
+        <v>1.5354</v>
       </c>
       <c r="H107" t="n">
-        <v>4.0527</v>
+        <v>4.0755</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9822</v>
       </c>
       <c r="F108" t="n">
-        <v>1.5011</v>
+        <v>0.5412</v>
       </c>
       <c r="G108" t="n">
-        <v>1.6148</v>
+        <v>1.3554</v>
       </c>
       <c r="H108" t="n">
-        <v>3.9548</v>
+        <v>3.7734</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.962</v>
       </c>
       <c r="F109" t="n">
-        <v>1.4859</v>
+        <v>0.503</v>
       </c>
       <c r="G109" t="n">
-        <v>1.5684</v>
+        <v>1.799</v>
       </c>
       <c r="H109" t="n">
-        <v>3.8942</v>
+        <v>3.9275</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.972</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>1.4971</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="G110" t="n">
-        <v>1.5976</v>
+        <v>1.5224</v>
       </c>
       <c r="H110" t="n">
-        <v>3.9389</v>
+        <v>3.8286</v>
       </c>
     </row>
     <row r="111">
@@ -3966,16 +3966,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.956</v>
+        <v>0.9538</v>
       </c>
       <c r="F111" t="n">
-        <v>1.466</v>
+        <v>0.5296</v>
       </c>
       <c r="G111" t="n">
-        <v>1.877</v>
+        <v>1.8955</v>
       </c>
       <c r="H111" t="n">
-        <v>3.8139</v>
+        <v>3.8207</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9789</v>
+        <v>0.9846</v>
       </c>
       <c r="F112" t="n">
-        <v>1.4028</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="G112" t="n">
-        <v>1.4349</v>
+        <v>1.2551</v>
       </c>
       <c r="H112" t="n">
-        <v>3.5458</v>
+        <v>3.495</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9792</v>
+        <v>0.9801</v>
       </c>
       <c r="F113" t="n">
-        <v>1.4231</v>
+        <v>0.5668</v>
       </c>
       <c r="G113" t="n">
-        <v>1.3957</v>
+        <v>1.3849</v>
       </c>
       <c r="H113" t="n">
-        <v>3.6341</v>
+        <v>3.6667</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9724</v>
+        <v>0.9769</v>
       </c>
       <c r="F114" t="n">
-        <v>1.4812</v>
+        <v>0.5316</v>
       </c>
       <c r="G114" t="n">
-        <v>1.5799</v>
+        <v>1.4989</v>
       </c>
       <c r="H114" t="n">
-        <v>3.8757</v>
+        <v>3.8129</v>
       </c>
     </row>
     <row r="115">
@@ -4094,16 +4094,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9562</v>
+        <v>0.9538</v>
       </c>
       <c r="F115" t="n">
-        <v>1.468</v>
+        <v>0.5377</v>
       </c>
       <c r="G115" t="n">
-        <v>1.871</v>
+        <v>1.89</v>
       </c>
       <c r="H115" t="n">
-        <v>3.8219</v>
+        <v>3.7879</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.966</v>
+        <v>0.9811</v>
       </c>
       <c r="F116" t="n">
-        <v>1.2527</v>
+        <v>0.7306</v>
       </c>
       <c r="G116" t="n">
-        <v>1.5298</v>
+        <v>1.1941</v>
       </c>
       <c r="H116" t="n">
-        <v>2.8087</v>
+        <v>2.8916</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9789</v>
+        <v>0.9808</v>
       </c>
       <c r="F117" t="n">
-        <v>1.2532</v>
+        <v>0.724</v>
       </c>
       <c r="G117" t="n">
-        <v>1.2371</v>
+        <v>1.2232</v>
       </c>
       <c r="H117" t="n">
-        <v>2.8115</v>
+        <v>2.9268</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9395</v>
+        <v>0.9651</v>
       </c>
       <c r="F118" t="n">
-        <v>1.5126</v>
+        <v>0.477</v>
       </c>
       <c r="G118" t="n">
-        <v>2.0955</v>
+        <v>1.6913</v>
       </c>
       <c r="H118" t="n">
-        <v>4</v>
+        <v>4.0289</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9792</v>
+        <v>0.9801</v>
       </c>
       <c r="F119" t="n">
-        <v>1.4231</v>
+        <v>0.5668</v>
       </c>
       <c r="G119" t="n">
-        <v>1.3957</v>
+        <v>1.3849</v>
       </c>
       <c r="H119" t="n">
-        <v>3.6341</v>
+        <v>3.6667</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9005</v>
+        <v>0.953</v>
       </c>
       <c r="F120" t="n">
-        <v>1.8044</v>
+        <v>0.265</v>
       </c>
       <c r="G120" t="n">
-        <v>2.6965</v>
+        <v>2.0374</v>
       </c>
       <c r="H120" t="n">
-        <v>5.0107</v>
+        <v>4.7761</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9005</v>
+        <v>0.953</v>
       </c>
       <c r="F121" t="n">
-        <v>1.8044</v>
+        <v>0.265</v>
       </c>
       <c r="G121" t="n">
-        <v>2.6965</v>
+        <v>2.0374</v>
       </c>
       <c r="H121" t="n">
-        <v>5.0107</v>
+        <v>4.7761</v>
       </c>
     </row>
     <row r="122">
@@ -4318,16 +4318,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.925</v>
+        <v>0.9319</v>
       </c>
       <c r="F122" t="n">
-        <v>1.6368</v>
+        <v>0.3863</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3772</v>
+        <v>2.2913</v>
       </c>
       <c r="H122" t="n">
-        <v>4.4583</v>
+        <v>4.3641</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9791</v>
+        <v>0.98</v>
       </c>
       <c r="F123" t="n">
-        <v>1.4233</v>
+        <v>0.5676</v>
       </c>
       <c r="G123" t="n">
-        <v>1.3968</v>
+        <v>1.3862</v>
       </c>
       <c r="H123" t="n">
-        <v>3.635</v>
+        <v>3.6631</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9765</v>
+        <v>0.976</v>
       </c>
       <c r="F124" t="n">
-        <v>1.4321</v>
+        <v>0.5405</v>
       </c>
       <c r="G124" t="n">
-        <v>1.4713</v>
+        <v>1.4971</v>
       </c>
       <c r="H124" t="n">
-        <v>3.6725</v>
+        <v>3.7764</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9338</v>
+        <v>0.8771</v>
       </c>
       <c r="F125" t="n">
-        <v>1.7774</v>
+        <v>0.1746</v>
       </c>
       <c r="G125" t="n">
-        <v>2.3725</v>
+        <v>2.997</v>
       </c>
       <c r="H125" t="n">
-        <v>4.926</v>
+        <v>5.0611</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8822</v>
+        <v>0.9498</v>
       </c>
       <c r="F126" t="n">
-        <v>1.7996</v>
+        <v>0.3015</v>
       </c>
       <c r="G126" t="n">
-        <v>2.969</v>
+        <v>2.1434</v>
       </c>
       <c r="H126" t="n">
-        <v>4.9958</v>
+        <v>4.6558</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9746</v>
       </c>
       <c r="F127" t="n">
-        <v>1.3428</v>
+        <v>0.6397</v>
       </c>
       <c r="G127" t="n">
-        <v>1.3453</v>
+        <v>1.3813</v>
       </c>
       <c r="H127" t="n">
-        <v>3.2713</v>
+        <v>3.3439</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.9506</v>
       </c>
       <c r="F128" t="n">
-        <v>1.8077</v>
+        <v>0.2956</v>
       </c>
       <c r="G128" t="n">
-        <v>3.0644</v>
+        <v>2.1324</v>
       </c>
       <c r="H128" t="n">
-        <v>5.0209</v>
+        <v>4.6757</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.9509</v>
       </c>
       <c r="F129" t="n">
-        <v>1.8048</v>
+        <v>0.2988</v>
       </c>
       <c r="G129" t="n">
-        <v>2.9585</v>
+        <v>2.1272</v>
       </c>
       <c r="H129" t="n">
-        <v>5.012</v>
+        <v>4.6648</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.8818</v>
+        <v>0.9505</v>
       </c>
       <c r="F130" t="n">
-        <v>1.8043</v>
+        <v>0.2928</v>
       </c>
       <c r="G130" t="n">
-        <v>2.9664</v>
+        <v>2.1319</v>
       </c>
       <c r="H130" t="n">
-        <v>5.0105</v>
+        <v>4.685</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.8784</v>
+        <v>0.9503</v>
       </c>
       <c r="F131" t="n">
-        <v>1.796</v>
+        <v>0.2926</v>
       </c>
       <c r="G131" t="n">
-        <v>2.9992</v>
+        <v>2.1309</v>
       </c>
       <c r="H131" t="n">
-        <v>4.9844</v>
+        <v>4.6856</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.8797</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>1.8079</v>
+        <v>0.3088</v>
       </c>
       <c r="G132" t="n">
-        <v>2.9788</v>
+        <v>1.8247</v>
       </c>
       <c r="H132" t="n">
-        <v>5.0217</v>
+        <v>4.6314</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8746</v>
+        <v>0.9684</v>
       </c>
       <c r="F133" t="n">
-        <v>1.8143</v>
+        <v>0.3058</v>
       </c>
       <c r="G133" t="n">
-        <v>3.068</v>
+        <v>1.814</v>
       </c>
       <c r="H133" t="n">
-        <v>5.0416</v>
+        <v>4.6415</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.8843</v>
+        <v>0.969</v>
       </c>
       <c r="F134" t="n">
-        <v>1.8082</v>
+        <v>0.2991</v>
       </c>
       <c r="G134" t="n">
-        <v>2.9551</v>
+        <v>1.7891</v>
       </c>
       <c r="H134" t="n">
-        <v>5.0227</v>
+        <v>4.6637</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.8748</v>
+        <v>0.9507</v>
       </c>
       <c r="F135" t="n">
-        <v>1.8076</v>
+        <v>0.2947</v>
       </c>
       <c r="G135" t="n">
-        <v>3.0649</v>
+        <v>2.1334</v>
       </c>
       <c r="H135" t="n">
-        <v>5.0207</v>
+        <v>4.6785</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.8786</v>
+        <v>0.9497</v>
       </c>
       <c r="F136" t="n">
-        <v>1.7947</v>
+        <v>0.2924</v>
       </c>
       <c r="G136" t="n">
-        <v>2.9933</v>
+        <v>2.1309</v>
       </c>
       <c r="H136" t="n">
-        <v>4.9803</v>
+        <v>4.6861</v>
       </c>
     </row>
     <row r="137">
@@ -4798,16 +4798,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9645</v>
+        <v>0.9676</v>
       </c>
       <c r="F137" t="n">
-        <v>1.7287</v>
+        <v>0.349</v>
       </c>
       <c r="G137" t="n">
-        <v>1.9431</v>
+        <v>1.8683</v>
       </c>
       <c r="H137" t="n">
-        <v>4.769</v>
+        <v>4.4947</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9627</v>
+        <v>0.9463</v>
       </c>
       <c r="F138" t="n">
-        <v>1.669</v>
+        <v>0.3499</v>
       </c>
       <c r="G138" t="n">
-        <v>1.9674</v>
+        <v>2.278</v>
       </c>
       <c r="H138" t="n">
-        <v>4.5695</v>
+        <v>4.4918</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.952</v>
+        <v>0.9673</v>
       </c>
       <c r="F139" t="n">
-        <v>1.7377</v>
+        <v>0.3623</v>
       </c>
       <c r="G139" t="n">
-        <v>2.1509</v>
+        <v>1.8488</v>
       </c>
       <c r="H139" t="n">
-        <v>4.7985</v>
+        <v>4.4487</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.971</v>
+        <v>0.981</v>
       </c>
       <c r="F140" t="n">
-        <v>1.3654</v>
+        <v>0.6076</v>
       </c>
       <c r="G140" t="n">
-        <v>1.6048</v>
+        <v>1.3899</v>
       </c>
       <c r="H140" t="n">
-        <v>3.3773</v>
+        <v>3.4896</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.985</v>
+        <v>0.9822</v>
       </c>
       <c r="F141" t="n">
-        <v>1.375</v>
+        <v>0.5851</v>
       </c>
       <c r="G141" t="n">
-        <v>1.2809</v>
+        <v>1.4229</v>
       </c>
       <c r="H141" t="n">
-        <v>3.4213</v>
+        <v>3.5882</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9627</v>
+        <v>0.9463</v>
       </c>
       <c r="F142" t="n">
-        <v>1.669</v>
+        <v>0.3499</v>
       </c>
       <c r="G142" t="n">
-        <v>1.9674</v>
+        <v>2.278</v>
       </c>
       <c r="H142" t="n">
-        <v>4.5695</v>
+        <v>4.4918</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9346</v>
+        <v>0.967</v>
       </c>
       <c r="F143" t="n">
-        <v>1.7283</v>
+        <v>0.3775</v>
       </c>
       <c r="G143" t="n">
-        <v>2.423</v>
+        <v>1.8658</v>
       </c>
       <c r="H143" t="n">
-        <v>4.7677</v>
+        <v>4.3955</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9706</v>
+        <v>0.968</v>
       </c>
       <c r="F144" t="n">
-        <v>1.7197</v>
+        <v>0.3757</v>
       </c>
       <c r="G144" t="n">
-        <v>1.7568</v>
+        <v>1.8452</v>
       </c>
       <c r="H144" t="n">
-        <v>4.7397</v>
+        <v>4.4015</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.985</v>
+        <v>0.9822</v>
       </c>
       <c r="F145" t="n">
-        <v>1.375</v>
+        <v>0.5851</v>
       </c>
       <c r="G145" t="n">
-        <v>1.2809</v>
+        <v>1.4229</v>
       </c>
       <c r="H145" t="n">
-        <v>3.4213</v>
+        <v>3.5882</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.9721</v>
+        <v>0.9806</v>
       </c>
       <c r="F146" t="n">
-        <v>1.3388</v>
+        <v>0.6519</v>
       </c>
       <c r="G146" t="n">
-        <v>1.4527</v>
+        <v>1.2364</v>
       </c>
       <c r="H146" t="n">
-        <v>3.2518</v>
+        <v>3.2868</v>
       </c>
     </row>
     <row r="147">
@@ -5118,16 +5118,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.9826</v>
+        <v>0.9801</v>
       </c>
       <c r="F147" t="n">
-        <v>1.3362</v>
+        <v>0.6476</v>
       </c>
       <c r="G147" t="n">
-        <v>1.1804</v>
+        <v>1.2362</v>
       </c>
       <c r="H147" t="n">
-        <v>3.2395</v>
+        <v>3.3069</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.9779</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F148" t="n">
-        <v>1.3398</v>
+        <v>0.6456</v>
       </c>
       <c r="G148" t="n">
-        <v>1.3279</v>
+        <v>1.2419</v>
       </c>
       <c r="H148" t="n">
-        <v>3.2568</v>
+        <v>3.3166</v>
       </c>
     </row>
     <row r="149">
@@ -5182,16 +5182,16 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.9772</v>
+        <v>0.974</v>
       </c>
       <c r="F149" t="n">
-        <v>1.3459</v>
+        <v>0.6279</v>
       </c>
       <c r="G149" t="n">
-        <v>1.3481</v>
+        <v>1.4034</v>
       </c>
       <c r="H149" t="n">
-        <v>3.2857</v>
+        <v>3.3984</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9807</v>
       </c>
       <c r="F150" t="n">
-        <v>1.3404</v>
+        <v>0.6415</v>
       </c>
       <c r="G150" t="n">
-        <v>1.3216</v>
+        <v>1.2293</v>
       </c>
       <c r="H150" t="n">
-        <v>3.2596</v>
+        <v>3.3358</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9806</v>
       </c>
       <c r="F151" t="n">
-        <v>1.3411</v>
+        <v>0.6425</v>
       </c>
       <c r="G151" t="n">
-        <v>1.3179</v>
+        <v>1.2301</v>
       </c>
       <c r="H151" t="n">
-        <v>3.263</v>
+        <v>3.331</v>
       </c>
     </row>
     <row r="152">
@@ -5278,16 +5278,16 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.9836</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F152" t="n">
-        <v>1.3352</v>
+        <v>0.6461</v>
       </c>
       <c r="G152" t="n">
-        <v>1.1445</v>
+        <v>1.243</v>
       </c>
       <c r="H152" t="n">
-        <v>3.2344</v>
+        <v>3.3141</v>
       </c>
     </row>
     <row r="153">
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.9842</v>
+        <v>0.9805</v>
       </c>
       <c r="F153" t="n">
-        <v>1.3379</v>
+        <v>0.6475</v>
       </c>
       <c r="G153" t="n">
-        <v>1.1358</v>
+        <v>1.2346</v>
       </c>
       <c r="H153" t="n">
-        <v>3.2475</v>
+        <v>3.3077</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.9741</v>
+        <v>0.9808</v>
       </c>
       <c r="F154" t="n">
-        <v>1.339</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="G154" t="n">
-        <v>1.4144</v>
+        <v>1.2416</v>
       </c>
       <c r="H154" t="n">
-        <v>3.2529</v>
+        <v>3.3258</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9676</v>
+        <v>0.9812</v>
       </c>
       <c r="F155" t="n">
-        <v>1.2553</v>
+        <v>0.7393</v>
       </c>
       <c r="G155" t="n">
-        <v>1.4842</v>
+        <v>1.1594</v>
       </c>
       <c r="H155" t="n">
-        <v>2.8228</v>
+        <v>2.8441</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9853</v>
+        <v>0.9789</v>
       </c>
       <c r="F156" t="n">
-        <v>1.2505</v>
+        <v>0.739</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0314</v>
+        <v>1.2473</v>
       </c>
       <c r="H156" t="n">
-        <v>2.7964</v>
+        <v>2.8462</v>
       </c>
     </row>
     <row r="157">
@@ -5434,20 +5434,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9847</v>
+        <v>0.9804</v>
       </c>
       <c r="F157" t="n">
-        <v>1.2463</v>
+        <v>0.7357</v>
       </c>
       <c r="G157" t="n">
-        <v>1.0346</v>
+        <v>1.201</v>
       </c>
       <c r="H157" t="n">
-        <v>2.7726</v>
+        <v>2.864</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9757</v>
+        <v>0.9756</v>
       </c>
       <c r="F158" t="n">
-        <v>1.2355</v>
+        <v>0.7749</v>
       </c>
       <c r="G158" t="n">
-        <v>1.3282</v>
+        <v>1.3279</v>
       </c>
       <c r="H158" t="n">
-        <v>2.7111</v>
+        <v>2.6429</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8824</v>
+        <v>0.9697</v>
       </c>
       <c r="F159" t="n">
-        <v>1.8155</v>
+        <v>0.2925</v>
       </c>
       <c r="G159" t="n">
-        <v>3.0298</v>
+        <v>1.8277</v>
       </c>
       <c r="H159" t="n">
-        <v>5.0451</v>
+        <v>4.6857</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.9752</v>
+        <v>0.9802</v>
       </c>
       <c r="F160" t="n">
-        <v>1.4205</v>
+        <v>0.5306</v>
       </c>
       <c r="G160" t="n">
-        <v>1.5211</v>
+        <v>1.3762</v>
       </c>
       <c r="H160" t="n">
-        <v>3.6229</v>
+        <v>3.8167</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.9756</v>
+        <v>0.9792</v>
       </c>
       <c r="F161" t="n">
-        <v>1.4196</v>
+        <v>0.5299</v>
       </c>
       <c r="G161" t="n">
-        <v>1.5019</v>
+        <v>1.3914</v>
       </c>
       <c r="H161" t="n">
-        <v>3.6188</v>
+        <v>3.8198</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.8917</v>
+        <v>0.9719</v>
       </c>
       <c r="F162" t="n">
-        <v>1.8208</v>
+        <v>0.2815</v>
       </c>
       <c r="G162" t="n">
-        <v>2.8866</v>
+        <v>1.7282</v>
       </c>
       <c r="H162" t="n">
-        <v>5.0614</v>
+        <v>4.7222</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9722</v>
+        <v>0.9719</v>
       </c>
       <c r="F163" t="n">
-        <v>1.6807</v>
+        <v>0.3315</v>
       </c>
       <c r="G163" t="n">
-        <v>1.8066</v>
+        <v>1.8213</v>
       </c>
       <c r="H163" t="n">
-        <v>4.6095</v>
+        <v>4.5547</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9708</v>
+        <v>0.9809</v>
       </c>
       <c r="F164" t="n">
-        <v>1.3655</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="G164" t="n">
-        <v>1.6055</v>
+        <v>1.3915</v>
       </c>
       <c r="H164" t="n">
-        <v>3.3775</v>
+        <v>3.4905</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9338</v>
+        <v>0.8771</v>
       </c>
       <c r="F165" t="n">
-        <v>1.7774</v>
+        <v>0.1746</v>
       </c>
       <c r="G165" t="n">
-        <v>2.3725</v>
+        <v>2.997</v>
       </c>
       <c r="H165" t="n">
-        <v>4.926</v>
+        <v>5.0611</v>
       </c>
     </row>
     <row r="166">
@@ -5722,20 +5722,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.9615</v>
+        <v>0.8193</v>
       </c>
       <c r="F166" t="n">
-        <v>1.9217</v>
+        <v>0.0476</v>
       </c>
       <c r="G166" t="n">
-        <v>2.1027</v>
+        <v>3.7102</v>
       </c>
       <c r="H166" t="n">
-        <v>5.3637</v>
+        <v>5.4366</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9756</v>
       </c>
       <c r="F167" t="n">
-        <v>1.6665</v>
+        <v>0.3458</v>
       </c>
       <c r="G167" t="n">
-        <v>1.7323</v>
+        <v>1.7111</v>
       </c>
       <c r="H167" t="n">
-        <v>4.561</v>
+        <v>4.5057</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9731</v>
+        <v>0.971</v>
       </c>
       <c r="F168" t="n">
-        <v>1.3418</v>
+        <v>0.6318</v>
       </c>
       <c r="G168" t="n">
-        <v>1.5537</v>
+        <v>1.6307</v>
       </c>
       <c r="H168" t="n">
-        <v>3.2664</v>
+        <v>3.3805</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9853</v>
+        <v>0.9838</v>
       </c>
       <c r="F169" t="n">
-        <v>1.2347</v>
+        <v>0.7367</v>
       </c>
       <c r="G169" t="n">
-        <v>1.0888</v>
+        <v>1.1378</v>
       </c>
       <c r="H169" t="n">
-        <v>2.7066</v>
+        <v>2.8587</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.971</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F170" t="n">
-        <v>1.4716</v>
+        <v>0.4699</v>
       </c>
       <c r="G170" t="n">
-        <v>1.8154</v>
+        <v>1.5687</v>
       </c>
       <c r="H170" t="n">
-        <v>3.8368</v>
+        <v>4.0559</v>
       </c>
     </row>
     <row r="171">
@@ -5886,16 +5886,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9812</v>
+        <v>0.9831</v>
       </c>
       <c r="F171" t="n">
-        <v>1.3002</v>
+        <v>0.6695</v>
       </c>
       <c r="G171" t="n">
-        <v>1.2732</v>
+        <v>1.3116</v>
       </c>
       <c r="H171" t="n">
-        <v>3.0612</v>
+        <v>3.2024</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9645</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>1.7097</v>
+        <v>0.3584</v>
       </c>
       <c r="G172" t="n">
-        <v>1.9133</v>
+        <v>1.6243</v>
       </c>
       <c r="H172" t="n">
-        <v>4.7066</v>
+        <v>4.4622</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
